--- a/Design-Files/SM_Top_Board_v3.3/BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Design-Files/SM_Top_Board_v3.3/BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ColeBenson-SmartMotors\Design-Files\SM_Top_Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ColeBenson-SmartMotors\Design-Files\SM_Top_Board_v3.3\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="448">
   <si>
     <t>Component list</t>
   </si>
@@ -82,12 +82,6 @@
     <t>C42</t>
   </si>
   <si>
-    <t>C48</t>
-  </si>
-  <si>
-    <t>C49</t>
-  </si>
-  <si>
     <t>C50</t>
   </si>
   <si>
@@ -271,9 +265,6 @@
     <t>CAP TANT 100UF 20% 25V 2917</t>
   </si>
   <si>
-    <t>470uF ±20% 50V 12.5mm 13.5mm 1000hrs 105℃ -40℃~+105℃ SMD,12.5x13.5mm Aluminum Electrolytic Capacitors - SMD RoHS</t>
-  </si>
-  <si>
     <t>CAP CER 470pF 10% X7R 50V 0603 SMD</t>
   </si>
   <si>
@@ -313,9 +304,6 @@
     <t>Test Point ON</t>
   </si>
   <si>
-    <t>CONN HEADER VERT 2POS 2.54MM</t>
-  </si>
-  <si>
     <t>RES SMD 5.1K OHM 5% 1/10W 0603</t>
   </si>
   <si>
@@ -421,9 +409,6 @@
     <t>CAP- 2917</t>
   </si>
   <si>
-    <t>VT1H471MI135000CE0</t>
-  </si>
-  <si>
     <t>CUS10S30,H3F</t>
   </si>
   <si>
@@ -454,9 +439,6 @@
     <t>TEST POINT</t>
   </si>
   <si>
-    <t>HDR1X2</t>
-  </si>
-  <si>
     <t>Res0603</t>
   </si>
   <si>
@@ -625,9 +607,6 @@
     <t>Wurth Electronics</t>
   </si>
   <si>
-    <t>Changzhou Huawei Elec</t>
-  </si>
-  <si>
     <t>Toshiba</t>
   </si>
   <si>
@@ -736,9 +715,6 @@
     <t>100uF</t>
   </si>
   <si>
-    <t>470uF</t>
-  </si>
-  <si>
     <t>470pF</t>
   </si>
   <si>
@@ -977,9 +953,6 @@
   </si>
   <si>
     <t>C7230</t>
-  </si>
-  <si>
-    <t>C191227</t>
   </si>
   <si>
     <t>C107092</t>
@@ -1383,12 +1356,6 @@
     <t>C178594</t>
   </si>
   <si>
-    <t>C492401</t>
-  </si>
-  <si>
-    <t>PZ254V-11-02P</t>
-  </si>
-  <si>
     <t>Ali-E</t>
   </si>
   <si>
@@ -1434,9 +1401,6 @@
     <t>Molex</t>
   </si>
   <si>
-    <t>P7, P8</t>
-  </si>
-  <si>
     <t>Q1, Q2, Q3, Q4</t>
   </si>
   <si>
@@ -1516,6 +1480,24 @@
   </si>
   <si>
     <t>C2, C13, C15, C20, C40, C51, C52, C53, C54, C55, C61, CF1, CF2, Cx1, Cx2</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>A1251WV-02P</t>
+  </si>
+  <si>
+    <t>1x2P 1 1.25mm Male pin 2 -25℃~+85℃ 1A Straight Plugin,P=1.25mm Wire To Board / Wire To Wire Connector ROHS</t>
+  </si>
+  <si>
+    <t>HR(Joint Tech Elec)</t>
+  </si>
+  <si>
+    <t>C462105</t>
+  </si>
+  <si>
+    <t>C48, C49</t>
   </si>
 </sst>
 </file>
@@ -2032,7 +2014,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2162,9 +2144,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2275,9 +2254,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2336,6 +2312,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2679,7 +2658,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V90"/>
+  <dimension ref="A1:Z91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -2700,6 +2679,7 @@
     <col min="18" max="18" width="29.42578125" customWidth="1"/>
     <col min="20" max="20" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2714,14 +2694,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2731,8 +2711,8 @@
         <v>0</v>
       </c>
       <c r="E2" s="10"/>
-      <c r="F2" s="51" t="s">
-        <v>286</v>
+      <c r="F2" s="50" t="s">
+        <v>278</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -2755,8 +2735,8 @@
         <v>1</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="52" t="s">
-        <v>284</v>
+      <c r="F3" s="51" t="s">
+        <v>276</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
@@ -2769,7 +2749,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="109"/>
+      <c r="R3" s="107"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2779,8 +2759,8 @@
         <v>2</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="53" t="s">
-        <v>285</v>
+      <c r="F4" s="52" t="s">
+        <v>277</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
@@ -2788,12 +2768,12 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
-      <c r="P4" s="57"/>
-      <c r="Q4" s="57"/>
-      <c r="R4" s="110"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="108"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2803,19 +2783,19 @@
         <v>3</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="54"/>
+      <c r="F5" s="53"/>
       <c r="G5" s="14"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
-      <c r="P5" s="57"/>
-      <c r="Q5" s="57"/>
-      <c r="R5" s="110"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="108"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2830,12 +2810,12 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
-      <c r="P6" s="57"/>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="110"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="108"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2855,7 +2835,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="110"/>
+      <c r="R7" s="108"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2875,7 +2855,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="110"/>
+      <c r="R8" s="108"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2883,86 +2863,86 @@
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="H9" s="100" t="s">
-        <v>188</v>
+        <v>144</v>
+      </c>
+      <c r="H9" s="98" t="s">
+        <v>182</v>
       </c>
       <c r="I9" s="29" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M9" s="31" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="O9" s="31" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="P9" s="31" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="Q9" s="31" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="R9" s="31" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="50">
+      <c r="B10" s="109">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="55" t="s">
-        <v>269</v>
+      <c r="C10" s="54" t="s">
+        <v>261</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -2974,8 +2954,8 @@
       <c r="N10" s="39">
         <v>22</v>
       </c>
-      <c r="O10" s="58" t="s">
-        <v>294</v>
+      <c r="O10" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P10" s="39">
         <v>0.38819999999999999</v>
@@ -2986,106 +2966,106 @@
       </c>
       <c r="R10" s="39"/>
     </row>
-    <row r="11" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="50">
+      <c r="B11" s="109">
         <f t="shared" ref="B11:B74" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="D11" s="83" t="s">
-        <v>453</v>
-      </c>
-      <c r="E11" s="80" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="79" t="s">
-        <v>123</v>
-      </c>
-      <c r="G11" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="H11" s="98" t="s">
-        <v>189</v>
-      </c>
-      <c r="I11" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J11" s="79" t="s">
-        <v>295</v>
-      </c>
-      <c r="K11" s="80" t="s">
-        <v>219</v>
-      </c>
-      <c r="L11" s="79">
+      <c r="C11" s="77" t="s">
+        <v>261</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>441</v>
+      </c>
+      <c r="E11" s="79" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="78" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="79" t="s">
+        <v>145</v>
+      </c>
+      <c r="H11" s="96" t="s">
+        <v>183</v>
+      </c>
+      <c r="I11" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J11" s="78" t="s">
+        <v>287</v>
+      </c>
+      <c r="K11" s="79" t="s">
+        <v>212</v>
+      </c>
+      <c r="L11" s="78">
         <v>15</v>
       </c>
-      <c r="M11" s="73">
+      <c r="M11" s="72">
         <f>L11*20</f>
         <v>300</v>
       </c>
-      <c r="N11" s="73">
+      <c r="N11" s="72">
         <v>400</v>
       </c>
-      <c r="O11" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P11" s="73">
+      <c r="O11" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P11" s="72">
         <v>1.4E-3</v>
       </c>
-      <c r="Q11" s="73">
+      <c r="Q11" s="72">
         <f>N11*P11</f>
         <v>0.55999999999999994</v>
       </c>
-      <c r="R11" s="73"/>
-    </row>
-    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R11" s="72"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="50">
+      <c r="B12" s="109">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="56" t="s">
-        <v>269</v>
+      <c r="C12" s="55" t="s">
+        <v>261</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="H12" s="101" t="s">
-        <v>190</v>
+        <v>146</v>
+      </c>
+      <c r="H12" s="99" t="s">
+        <v>184</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="L12" s="72">
+        <v>213</v>
+      </c>
+      <c r="L12" s="71">
         <v>2</v>
       </c>
       <c r="M12" s="39">
-        <f t="shared" ref="M12:M71" si="1">L12*20</f>
+        <f t="shared" ref="M12:M70" si="1">L12*20</f>
         <v>40</v>
       </c>
       <c r="N12" s="39">
         <v>100</v>
       </c>
-      <c r="O12" s="58" t="s">
-        <v>294</v>
+      <c r="O12" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P12" s="39">
         <v>1.2999999999999999E-3</v>
@@ -3094,95 +3074,95 @@
         <f t="shared" ref="Q12" si="2">P12*N12</f>
         <v>0.13</v>
       </c>
-      <c r="R12" s="69"/>
-    </row>
-    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R12" s="68"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="50">
+      <c r="B13" s="109">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="D13" s="79" t="s">
-        <v>372</v>
-      </c>
-      <c r="E13" s="80" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="79" t="s">
-        <v>124</v>
-      </c>
-      <c r="G13" s="80" t="s">
-        <v>153</v>
-      </c>
-      <c r="H13" s="98" t="s">
-        <v>191</v>
-      </c>
-      <c r="I13" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J13" s="79" t="s">
-        <v>297</v>
-      </c>
-      <c r="K13" s="80" t="s">
-        <v>221</v>
-      </c>
-      <c r="L13" s="83">
+      <c r="C13" s="77" t="s">
+        <v>261</v>
+      </c>
+      <c r="D13" s="78" t="s">
+        <v>363</v>
+      </c>
+      <c r="E13" s="79" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="78" t="s">
+        <v>120</v>
+      </c>
+      <c r="G13" s="79" t="s">
+        <v>147</v>
+      </c>
+      <c r="H13" s="96" t="s">
+        <v>185</v>
+      </c>
+      <c r="I13" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J13" s="78" t="s">
+        <v>289</v>
+      </c>
+      <c r="K13" s="79" t="s">
+        <v>214</v>
+      </c>
+      <c r="L13" s="82">
         <v>1</v>
       </c>
-      <c r="M13" s="73">
+      <c r="M13" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N13" s="88">
+      <c r="N13" s="87">
         <v>40</v>
       </c>
-      <c r="O13" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P13" s="73">
+      <c r="O13" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P13" s="72">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="Q13" s="73">
+      <c r="Q13" s="72">
         <f t="shared" ref="Q13" si="3">N13*P13</f>
         <v>1.4359999999999999</v>
       </c>
-      <c r="R13" s="69"/>
-    </row>
-    <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R13" s="68"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="50">
+      <c r="B14" s="109">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="56" t="s">
-        <v>269</v>
+      <c r="C14" s="55" t="s">
+        <v>261</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="H14" s="101" t="s">
-        <v>192</v>
+        <v>148</v>
+      </c>
+      <c r="H14" s="99" t="s">
+        <v>186</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="L14" s="37">
         <v>6</v>
@@ -3194,8 +3174,8 @@
       <c r="N14" s="39">
         <v>130</v>
       </c>
-      <c r="O14" s="58" t="s">
-        <v>294</v>
+      <c r="O14" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P14" s="39">
         <v>4.0899999999999999E-2</v>
@@ -3204,95 +3184,95 @@
         <f>P14*N14</f>
         <v>5.3170000000000002</v>
       </c>
-      <c r="R14" s="69"/>
-    </row>
-    <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R14" s="68"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="50">
+      <c r="B15" s="109">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="D15" s="79" t="s">
-        <v>397</v>
-      </c>
-      <c r="E15" s="80" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="79" t="s">
-        <v>123</v>
-      </c>
-      <c r="G15" s="80" t="s">
-        <v>155</v>
-      </c>
-      <c r="H15" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="I15" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J15" s="79" t="s">
-        <v>299</v>
-      </c>
-      <c r="K15" s="80" t="s">
-        <v>223</v>
-      </c>
-      <c r="L15" s="83">
+      <c r="C15" s="77" t="s">
+        <v>261</v>
+      </c>
+      <c r="D15" s="78" t="s">
+        <v>388</v>
+      </c>
+      <c r="E15" s="79" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="78" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="H15" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="I15" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J15" s="78" t="s">
+        <v>291</v>
+      </c>
+      <c r="K15" s="79" t="s">
+        <v>216</v>
+      </c>
+      <c r="L15" s="82">
         <v>3</v>
       </c>
-      <c r="M15" s="73">
+      <c r="M15" s="72">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="N15" s="88">
+      <c r="N15" s="87">
         <v>100</v>
       </c>
-      <c r="O15" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P15" s="73">
+      <c r="O15" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P15" s="72">
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="Q15" s="73">
+      <c r="Q15" s="72">
         <f t="shared" ref="Q15" si="4">N15*P15</f>
         <v>0.59</v>
       </c>
-      <c r="R15" s="69"/>
-    </row>
-    <row r="16" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R15" s="68"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="50">
+      <c r="B16" s="109">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="56" t="s">
-        <v>269</v>
+      <c r="C16" s="55" t="s">
+        <v>261</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="G16" s="77" t="s">
-        <v>375</v>
-      </c>
-      <c r="H16" s="102" t="s">
-        <v>192</v>
+        <v>119</v>
+      </c>
+      <c r="G16" s="76" t="s">
+        <v>366</v>
+      </c>
+      <c r="H16" s="100" t="s">
+        <v>186</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="L16" s="37">
         <v>6</v>
@@ -3304,8 +3284,8 @@
       <c r="N16" s="39">
         <v>130</v>
       </c>
-      <c r="O16" s="58" t="s">
-        <v>294</v>
+      <c r="O16" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P16" s="39">
         <v>3.32E-2</v>
@@ -3314,150 +3294,150 @@
         <f t="shared" ref="Q16" si="5">P16*N16</f>
         <v>4.3159999999999998</v>
       </c>
-      <c r="R16" s="69"/>
-    </row>
-    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R16" s="68"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="50">
+      <c r="B17" s="109">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="D17" s="79" t="s">
+      <c r="C17" s="77" t="s">
+        <v>261</v>
+      </c>
+      <c r="D17" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="80" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="79" t="s">
-        <v>123</v>
-      </c>
-      <c r="G17" s="80" t="s">
-        <v>156</v>
-      </c>
-      <c r="H17" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="I17" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J17" s="79" t="s">
-        <v>300</v>
-      </c>
-      <c r="K17" s="80" t="s">
-        <v>225</v>
-      </c>
-      <c r="L17" s="79">
+      <c r="E17" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="78" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="79" t="s">
+        <v>150</v>
+      </c>
+      <c r="H17" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="I17" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J17" s="78" t="s">
+        <v>292</v>
+      </c>
+      <c r="K17" s="79" t="s">
+        <v>218</v>
+      </c>
+      <c r="L17" s="78">
         <v>1</v>
       </c>
-      <c r="M17" s="73">
+      <c r="M17" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N17" s="73">
+      <c r="N17" s="72">
         <v>100</v>
       </c>
-      <c r="O17" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P17" s="73">
+      <c r="O17" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P17" s="72">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="Q17" s="73">
+      <c r="Q17" s="72">
         <f t="shared" ref="Q17" si="6">N17*P17</f>
         <v>0.31</v>
       </c>
-      <c r="R17" s="73"/>
-    </row>
-    <row r="18" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R17" s="72"/>
+    </row>
+    <row r="18" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="50">
+      <c r="B18" s="109">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="D18" s="79" t="s">
-        <v>307</v>
-      </c>
-      <c r="E18" s="80" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="79" t="s">
-        <v>125</v>
-      </c>
-      <c r="G18" s="86" t="s">
-        <v>157</v>
-      </c>
-      <c r="H18" s="98" t="s">
-        <v>193</v>
-      </c>
-      <c r="I18" s="79" t="s">
-        <v>302</v>
-      </c>
-      <c r="J18" s="79" t="s">
-        <v>301</v>
-      </c>
-      <c r="K18" s="80" t="s">
-        <v>226</v>
-      </c>
-      <c r="L18" s="79">
+      <c r="C18" s="77" t="s">
+        <v>261</v>
+      </c>
+      <c r="D18" s="78" t="s">
+        <v>299</v>
+      </c>
+      <c r="E18" s="79" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="78" t="s">
+        <v>121</v>
+      </c>
+      <c r="G18" s="85" t="s">
+        <v>151</v>
+      </c>
+      <c r="H18" s="96" t="s">
+        <v>187</v>
+      </c>
+      <c r="I18" s="78" t="s">
+        <v>294</v>
+      </c>
+      <c r="J18" s="78" t="s">
+        <v>293</v>
+      </c>
+      <c r="K18" s="79" t="s">
+        <v>219</v>
+      </c>
+      <c r="L18" s="78">
         <v>8</v>
       </c>
-      <c r="M18" s="73">
+      <c r="M18" s="72">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N18" s="73">
+      <c r="N18" s="72">
         <v>180</v>
       </c>
-      <c r="O18" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P18" s="73">
+      <c r="O18" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P18" s="72">
         <v>3.09E-2</v>
       </c>
-      <c r="Q18" s="73">
+      <c r="Q18" s="72">
         <f t="shared" ref="Q18" si="7">N18*P18</f>
         <v>5.5620000000000003</v>
       </c>
-      <c r="R18" s="73"/>
-    </row>
-    <row r="19" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R18" s="72"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="50">
+      <c r="B19" s="109">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="56" t="s">
-        <v>269</v>
+      <c r="C19" s="55" t="s">
+        <v>261</v>
       </c>
       <c r="D19" s="37" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="G19" s="85" t="s">
-        <v>158</v>
-      </c>
-      <c r="H19" s="101" t="s">
-        <v>194</v>
+        <v>119</v>
+      </c>
+      <c r="G19" s="84" t="s">
+        <v>152</v>
+      </c>
+      <c r="H19" s="99" t="s">
+        <v>188</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="J19" s="37" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="K19" s="38" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="L19" s="37">
         <v>1</v>
@@ -3469,8 +3449,8 @@
       <c r="N19" s="39">
         <v>100</v>
       </c>
-      <c r="O19" s="58" t="s">
-        <v>294</v>
+      <c r="O19" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P19" s="39">
         <v>5.3E-3</v>
@@ -3481,148 +3461,148 @@
       </c>
       <c r="R19" s="39"/>
     </row>
-    <row r="20" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="50">
+      <c r="B20" s="109">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="D20" s="79" t="s">
+      <c r="C20" s="77" t="s">
+        <v>261</v>
+      </c>
+      <c r="D20" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="80" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="G20" s="79" t="s">
-        <v>126</v>
-      </c>
-      <c r="H20" s="98" t="s">
-        <v>195</v>
-      </c>
-      <c r="I20" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J20" s="79" t="s">
-        <v>305</v>
-      </c>
-      <c r="K20" s="80" t="s">
-        <v>218</v>
-      </c>
-      <c r="L20" s="79">
+      <c r="E20" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G20" s="78" t="s">
+        <v>122</v>
+      </c>
+      <c r="H20" s="96" t="s">
+        <v>189</v>
+      </c>
+      <c r="I20" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J20" s="78" t="s">
+        <v>297</v>
+      </c>
+      <c r="K20" s="79" t="s">
+        <v>211</v>
+      </c>
+      <c r="L20" s="78">
         <v>1</v>
       </c>
-      <c r="M20" s="73">
+      <c r="M20" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N20" s="73">
+      <c r="N20" s="72">
         <v>25</v>
       </c>
-      <c r="O20" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P20" s="73">
+      <c r="O20" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P20" s="72">
         <v>0.22189999999999999</v>
       </c>
-      <c r="Q20" s="73">
+      <c r="Q20" s="72">
         <f t="shared" ref="Q20" si="9">N20*P20</f>
         <v>5.5474999999999994</v>
       </c>
-      <c r="R20" s="73"/>
-    </row>
-    <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R20" s="72"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="50">
-        <f>ROW(B21) - ROW($B$9)</f>
+      <c r="B21" s="109">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="D21" s="79" t="s">
-        <v>412</v>
-      </c>
-      <c r="E21" s="80" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="79" t="s">
-        <v>123</v>
-      </c>
-      <c r="G21" s="80" t="s">
-        <v>162</v>
-      </c>
-      <c r="H21" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="I21" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J21" s="79" t="s">
-        <v>312</v>
-      </c>
-      <c r="K21" s="80" t="s">
-        <v>231</v>
-      </c>
-      <c r="L21" s="79">
+      <c r="C21" s="77" t="s">
+        <v>261</v>
+      </c>
+      <c r="D21" s="78" t="s">
+        <v>401</v>
+      </c>
+      <c r="E21" s="79" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" s="78" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" s="79" t="s">
+        <v>156</v>
+      </c>
+      <c r="H21" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="I21" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J21" s="78" t="s">
+        <v>304</v>
+      </c>
+      <c r="K21" s="79" t="s">
+        <v>224</v>
+      </c>
+      <c r="L21" s="78">
         <v>3</v>
       </c>
-      <c r="M21" s="73">
+      <c r="M21" s="72">
         <f>L21*20</f>
         <v>60</v>
       </c>
-      <c r="N21" s="73">
+      <c r="N21" s="72">
         <v>100</v>
       </c>
-      <c r="O21" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P21" s="73">
+      <c r="O21" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P21" s="72">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="Q21" s="73">
+      <c r="Q21" s="72">
         <f t="shared" ref="Q21" si="10">N21*P21</f>
         <v>0.32</v>
       </c>
-      <c r="R21" s="73"/>
-    </row>
-    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R21" s="72"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="50">
+      <c r="B22" s="109">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="56" t="s">
-        <v>269</v>
+      <c r="C22" s="55" t="s">
+        <v>261</v>
       </c>
       <c r="D22" s="37" t="s">
         <v>12</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="H22" s="101" t="s">
-        <v>189</v>
+        <v>153</v>
+      </c>
+      <c r="H22" s="99" t="s">
+        <v>183</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="L22" s="37">
         <v>2</v>
@@ -3634,8 +3614,8 @@
       <c r="N22" s="39">
         <v>100</v>
       </c>
-      <c r="O22" s="58" t="s">
-        <v>294</v>
+      <c r="O22" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P22" s="39">
         <v>7.7000000000000002E-3</v>
@@ -3646,38 +3626,38 @@
       </c>
       <c r="R22" s="39"/>
     </row>
-    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="50">
+      <c r="B23" s="109">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="56" t="s">
-        <v>269</v>
+      <c r="C23" s="55" t="s">
+        <v>261</v>
       </c>
       <c r="D23" s="37" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="H23" s="101" t="s">
-        <v>191</v>
+        <v>154</v>
+      </c>
+      <c r="H23" s="99" t="s">
+        <v>185</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J23" s="37" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="L23" s="37">
         <v>1</v>
@@ -3689,8 +3669,8 @@
       <c r="N23" s="39">
         <v>40</v>
       </c>
-      <c r="O23" s="58" t="s">
-        <v>294</v>
+      <c r="O23" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P23" s="39">
         <v>3.49E-2</v>
@@ -3701,93 +3681,93 @@
       </c>
       <c r="R23" s="39"/>
     </row>
-    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="50">
+      <c r="B24" s="109">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="D24" s="79" t="s">
-        <v>371</v>
-      </c>
-      <c r="E24" s="80" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="79" t="s">
-        <v>123</v>
-      </c>
-      <c r="G24" s="80" t="s">
-        <v>161</v>
-      </c>
-      <c r="H24" s="98" t="s">
-        <v>189</v>
-      </c>
-      <c r="I24" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J24" s="79" t="s">
-        <v>309</v>
-      </c>
-      <c r="K24" s="80" t="s">
-        <v>229</v>
-      </c>
-      <c r="L24" s="79">
+      <c r="C24" s="77" t="s">
+        <v>261</v>
+      </c>
+      <c r="D24" s="78" t="s">
+        <v>362</v>
+      </c>
+      <c r="E24" s="79" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" s="78" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="79" t="s">
+        <v>155</v>
+      </c>
+      <c r="H24" s="96" t="s">
+        <v>183</v>
+      </c>
+      <c r="I24" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J24" s="78" t="s">
+        <v>301</v>
+      </c>
+      <c r="K24" s="79" t="s">
+        <v>222</v>
+      </c>
+      <c r="L24" s="78">
         <v>1</v>
       </c>
-      <c r="M24" s="73">
+      <c r="M24" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N24" s="73">
+      <c r="N24" s="72">
         <v>40</v>
       </c>
-      <c r="O24" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P24" s="73">
+      <c r="O24" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P24" s="72">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="Q24" s="73">
+      <c r="Q24" s="72">
         <f t="shared" ref="Q24" si="13">N24*P24</f>
         <v>0.7679999999999999</v>
       </c>
-      <c r="R24" s="69"/>
-    </row>
-    <row r="25" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R24" s="68"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="50">
+      <c r="B25" s="109">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="56" t="s">
-        <v>269</v>
+      <c r="C25" s="55" t="s">
+        <v>261</v>
       </c>
       <c r="D25" s="37" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="G25" s="87">
+        <v>120</v>
+      </c>
+      <c r="G25" s="86">
         <v>885012205080</v>
       </c>
-      <c r="H25" s="101" t="s">
-        <v>196</v>
+      <c r="H25" s="99" t="s">
+        <v>190</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="J25" s="37" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="L25" s="37">
         <v>1</v>
@@ -3799,8 +3779,8 @@
       <c r="N25" s="39">
         <v>100</v>
       </c>
-      <c r="O25" s="58" t="s">
-        <v>294</v>
+      <c r="O25" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P25" s="39">
         <v>3.0000000000000001E-3</v>
@@ -3811,93 +3791,93 @@
       </c>
       <c r="R25" s="39"/>
     </row>
-    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="50">
+      <c r="B26" s="109">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="D26" s="79" t="s">
+      <c r="C26" s="77" t="s">
+        <v>261</v>
+      </c>
+      <c r="D26" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="82" t="s">
-        <v>373</v>
-      </c>
-      <c r="F26" s="79" t="s">
-        <v>123</v>
-      </c>
-      <c r="G26" s="82" t="s">
-        <v>394</v>
-      </c>
-      <c r="H26" s="103" t="s">
-        <v>207</v>
-      </c>
-      <c r="I26" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J26" s="79" t="s">
-        <v>374</v>
-      </c>
-      <c r="K26" s="82" t="s">
-        <v>384</v>
-      </c>
-      <c r="L26" s="79">
+      <c r="E26" s="81" t="s">
+        <v>364</v>
+      </c>
+      <c r="F26" s="78" t="s">
+        <v>119</v>
+      </c>
+      <c r="G26" s="81" t="s">
+        <v>385</v>
+      </c>
+      <c r="H26" s="101" t="s">
+        <v>200</v>
+      </c>
+      <c r="I26" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J26" s="78" t="s">
+        <v>365</v>
+      </c>
+      <c r="K26" s="81" t="s">
+        <v>375</v>
+      </c>
+      <c r="L26" s="78">
         <v>1</v>
       </c>
-      <c r="M26" s="73">
+      <c r="M26" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N26" s="73">
+      <c r="N26" s="72">
         <v>100</v>
       </c>
-      <c r="O26" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P26" s="73">
+      <c r="O26" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P26" s="72">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="Q26" s="73">
+      <c r="Q26" s="72">
         <f t="shared" ref="Q26" si="15">N26*P26</f>
         <v>0.33999999999999997</v>
       </c>
-      <c r="R26" s="69"/>
-    </row>
-    <row r="27" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R26" s="68"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="50">
+      <c r="B27" s="109">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="56" t="s">
-        <v>269</v>
+      <c r="C27" s="55" t="s">
+        <v>261</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="H27" s="101" t="s">
-        <v>192</v>
+        <v>157</v>
+      </c>
+      <c r="H27" s="99" t="s">
+        <v>186</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J27" s="37" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="L27" s="37">
         <v>1</v>
@@ -3909,8 +3889,8 @@
       <c r="N27" s="39">
         <v>30</v>
       </c>
-      <c r="O27" s="58" t="s">
-        <v>294</v>
+      <c r="O27" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P27" s="39">
         <v>0.2525</v>
@@ -3919,810 +3899,816 @@
         <f t="shared" ref="Q27" si="16">P27*N27</f>
         <v>7.5750000000000002</v>
       </c>
-      <c r="R27" s="70"/>
-    </row>
-    <row r="28" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R27" s="69"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="50">
+      <c r="B28" s="109">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="56" t="s">
-        <v>269</v>
+      <c r="C28" s="55" t="s">
+        <v>261</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>16</v>
+        <v>447</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="H28" s="101" t="s">
-        <v>193</v>
+        <v>158</v>
+      </c>
+      <c r="H28" s="99" t="s">
+        <v>187</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="L28" s="37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" s="39">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N28" s="39">
-        <v>22</v>
-      </c>
-      <c r="O28" s="58" t="s">
-        <v>294</v>
+        <v>41</v>
+      </c>
+      <c r="O28" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P28" s="39">
-        <v>0.89629999999999999</v>
+        <v>0.89410000000000001</v>
       </c>
       <c r="Q28" s="39">
         <f t="shared" ref="Q28" si="17">P28*N28</f>
-        <v>19.718599999999999</v>
+        <v>36.658099999999997</v>
       </c>
       <c r="R28" s="39"/>
     </row>
-    <row r="29" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="50">
+      <c r="B29" s="109">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="D29" s="79" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="80" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="G29" s="79" t="s">
-        <v>129</v>
-      </c>
-      <c r="H29" s="98" t="s">
-        <v>197</v>
-      </c>
-      <c r="I29" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J29" s="79" t="s">
-        <v>315</v>
-      </c>
-      <c r="K29" s="80" t="s">
-        <v>234</v>
-      </c>
-      <c r="L29" s="79">
+      <c r="C29" s="55" t="s">
+        <v>261</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="H29" s="99" t="s">
+        <v>184</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="K29" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="L29" s="37">
         <v>1</v>
       </c>
-      <c r="M29" s="73">
+      <c r="M29" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N29" s="73">
-        <v>21</v>
-      </c>
-      <c r="O29" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P29" s="73">
-        <v>0.47249999999999998</v>
-      </c>
-      <c r="Q29" s="73">
-        <f t="shared" ref="Q29" si="18">N29*P29</f>
-        <v>9.9224999999999994</v>
-      </c>
-      <c r="R29" s="73"/>
-    </row>
-    <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N29" s="39">
+        <v>100</v>
+      </c>
+      <c r="O29" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P29" s="39">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="Q29" s="39">
+        <f t="shared" ref="Q29" si="18">P29*N29</f>
+        <v>0.31</v>
+      </c>
+      <c r="R29" s="39"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="50">
+      <c r="B30" s="109">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="56" t="s">
-        <v>269</v>
+      <c r="C30" s="55" t="s">
+        <v>261</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>165</v>
-      </c>
-      <c r="H30" s="101" t="s">
-        <v>190</v>
+        <v>160</v>
+      </c>
+      <c r="H30" s="99" t="s">
+        <v>183</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="L30" s="37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M30" s="39">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N30" s="39">
         <v>100</v>
       </c>
-      <c r="O30" s="58" t="s">
-        <v>294</v>
+      <c r="O30" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P30" s="39">
-        <v>3.0999999999999999E-3</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="Q30" s="39">
         <f t="shared" ref="Q30" si="19">P30*N30</f>
-        <v>0.31</v>
+        <v>0.54999999999999993</v>
       </c>
       <c r="R30" s="39"/>
     </row>
-    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="50">
+      <c r="B31" s="109">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="56" t="s">
-        <v>269</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="G31" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="H31" s="101" t="s">
-        <v>189</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J31" s="37" t="s">
-        <v>317</v>
-      </c>
-      <c r="K31" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="L31" s="37">
-        <v>4</v>
-      </c>
-      <c r="M31" s="39">
+      <c r="C31" s="77" t="s">
+        <v>262</v>
+      </c>
+      <c r="D31" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="79" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G31" s="79" t="s">
+        <v>125</v>
+      </c>
+      <c r="H31" s="96" t="s">
+        <v>191</v>
+      </c>
+      <c r="I31" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J31" s="78" t="s">
+        <v>309</v>
+      </c>
+      <c r="K31" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L31" s="78">
+        <v>1</v>
+      </c>
+      <c r="M31" s="72">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N31" s="39">
-        <v>100</v>
-      </c>
-      <c r="O31" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P31" s="39">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="Q31" s="39">
-        <f t="shared" ref="Q31" si="20">P31*N31</f>
-        <v>0.54999999999999993</v>
-      </c>
-      <c r="R31" s="39"/>
-    </row>
-    <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="N31" s="72">
+        <v>30</v>
+      </c>
+      <c r="O31" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P31" s="72">
+        <v>4.87E-2</v>
+      </c>
+      <c r="Q31" s="72">
+        <f t="shared" ref="Q31" si="20">N31*P31</f>
+        <v>1.4610000000000001</v>
+      </c>
+      <c r="R31" s="72"/>
+    </row>
+    <row r="32" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="50">
+      <c r="B32" s="109">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="78" t="s">
-        <v>270</v>
-      </c>
-      <c r="D32" s="79" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="80" t="s">
-        <v>82</v>
-      </c>
-      <c r="F32" s="79" t="s">
+      <c r="C32" s="55" t="s">
         <v>262</v>
       </c>
-      <c r="G32" s="80" t="s">
-        <v>130</v>
-      </c>
-      <c r="H32" s="98" t="s">
-        <v>198</v>
-      </c>
-      <c r="I32" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J32" s="79" t="s">
-        <v>318</v>
-      </c>
-      <c r="K32" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L32" s="79">
+      <c r="D32" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="G32" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="H32" s="99" t="s">
+        <v>192</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>310</v>
+      </c>
+      <c r="K32" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L32" s="37">
         <v>1</v>
       </c>
-      <c r="M32" s="73">
+      <c r="M32" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N32" s="73">
+      <c r="N32" s="39">
         <v>30</v>
       </c>
-      <c r="O32" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P32" s="73">
-        <v>4.87E-2</v>
-      </c>
-      <c r="Q32" s="73">
-        <f t="shared" ref="Q32" si="21">N32*P32</f>
-        <v>1.4610000000000001</v>
-      </c>
-      <c r="R32" s="73"/>
-    </row>
-    <row r="33" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O32" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P32" s="39">
+        <v>7.4300000000000005E-2</v>
+      </c>
+      <c r="Q32" s="39">
+        <f t="shared" ref="Q32" si="21">P32*N32</f>
+        <v>2.2290000000000001</v>
+      </c>
+      <c r="R32" s="39"/>
+    </row>
+    <row r="33" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="50">
+      <c r="B33" s="109">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="56" t="s">
-        <v>270</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="G33" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="H33" s="101" t="s">
-        <v>199</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J33" s="37" t="s">
-        <v>319</v>
-      </c>
-      <c r="K33" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="L33" s="37">
-        <v>1</v>
-      </c>
-      <c r="M33" s="39">
+      <c r="C33" s="77" t="s">
+        <v>262</v>
+      </c>
+      <c r="D33" s="78" t="s">
+        <v>390</v>
+      </c>
+      <c r="E33" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="G33" s="79" t="s">
+        <v>230</v>
+      </c>
+      <c r="H33" s="96" t="s">
+        <v>192</v>
+      </c>
+      <c r="I33" s="78" t="s">
+        <v>230</v>
+      </c>
+      <c r="J33" s="78" t="s">
+        <v>311</v>
+      </c>
+      <c r="K33" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L33" s="78">
+        <v>2</v>
+      </c>
+      <c r="M33" s="72">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N33" s="39">
-        <v>30</v>
-      </c>
-      <c r="O33" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P33" s="39">
-        <v>7.4300000000000005E-2</v>
-      </c>
-      <c r="Q33" s="39">
-        <f t="shared" ref="Q33" si="22">P33*N33</f>
-        <v>2.2290000000000001</v>
-      </c>
-      <c r="R33" s="39"/>
-    </row>
-    <row r="34" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="N33" s="72">
+        <v>60</v>
+      </c>
+      <c r="O33" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P33" s="72">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="Q33" s="72">
+        <f t="shared" ref="Q33" si="22">N33*P33</f>
+        <v>1.734</v>
+      </c>
+      <c r="R33" s="69"/>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="50">
+      <c r="B34" s="109">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="78" t="s">
-        <v>270</v>
-      </c>
-      <c r="D34" s="79" t="s">
-        <v>399</v>
-      </c>
-      <c r="E34" s="80" t="s">
-        <v>84</v>
-      </c>
-      <c r="F34" s="79" t="s">
-        <v>131</v>
-      </c>
-      <c r="G34" s="80" t="s">
-        <v>238</v>
-      </c>
-      <c r="H34" s="98" t="s">
-        <v>199</v>
-      </c>
-      <c r="I34" s="79" t="s">
-        <v>238</v>
-      </c>
-      <c r="J34" s="79" t="s">
-        <v>320</v>
-      </c>
-      <c r="K34" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L34" s="79">
+      <c r="C34" s="89" t="s">
+        <v>262</v>
+      </c>
+      <c r="D34" s="90" t="s">
+        <v>376</v>
+      </c>
+      <c r="E34" s="91" t="s">
+        <v>419</v>
+      </c>
+      <c r="F34" s="91" t="s">
+        <v>254</v>
+      </c>
+      <c r="G34" s="91" t="s">
+        <v>416</v>
+      </c>
+      <c r="H34" s="102" t="s">
+        <v>420</v>
+      </c>
+      <c r="I34" s="91" t="s">
+        <v>259</v>
+      </c>
+      <c r="J34" s="91" t="s">
+        <v>435</v>
+      </c>
+      <c r="K34" s="92" t="s">
+        <v>259</v>
+      </c>
+      <c r="L34" s="91">
+        <v>8</v>
+      </c>
+      <c r="M34" s="92">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="N34" s="72">
+        <v>165</v>
+      </c>
+      <c r="O34" s="93" t="s">
+        <v>286</v>
+      </c>
+      <c r="P34" s="92">
+        <v>0.14319999999999999</v>
+      </c>
+      <c r="Q34" s="92">
+        <f t="shared" ref="Q34:Q35" si="23">P34*N34</f>
+        <v>23.628</v>
+      </c>
+      <c r="R34" s="94"/>
+    </row>
+    <row r="35" spans="1:26" s="95" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="88"/>
+      <c r="B35" s="109">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C35" s="77" t="s">
+        <v>262</v>
+      </c>
+      <c r="D35" s="78" t="s">
+        <v>408</v>
+      </c>
+      <c r="E35" s="78" t="s">
+        <v>409</v>
+      </c>
+      <c r="F35" s="78" t="s">
+        <v>410</v>
+      </c>
+      <c r="G35" s="78" t="s">
+        <v>411</v>
+      </c>
+      <c r="H35" s="96" t="s">
+        <v>193</v>
+      </c>
+      <c r="I35" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J35" s="78" t="s">
+        <v>436</v>
+      </c>
+      <c r="K35" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="L35" s="78">
         <v>2</v>
       </c>
-      <c r="M34" s="73">
+      <c r="M35" s="92">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N34" s="73">
-        <v>60</v>
-      </c>
-      <c r="O34" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P34" s="73">
-        <v>2.8899999999999999E-2</v>
-      </c>
-      <c r="Q34" s="73">
-        <f t="shared" ref="Q34" si="23">N34*P34</f>
-        <v>1.734</v>
-      </c>
-      <c r="R34" s="70"/>
-    </row>
-    <row r="35" spans="1:22" s="97" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="89"/>
-      <c r="B35" s="90">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C35" s="91" t="s">
-        <v>270</v>
-      </c>
-      <c r="D35" s="92" t="s">
-        <v>385</v>
-      </c>
-      <c r="E35" s="93" t="s">
-        <v>431</v>
-      </c>
-      <c r="F35" s="93" t="s">
-        <v>262</v>
-      </c>
-      <c r="G35" s="93" t="s">
-        <v>428</v>
-      </c>
-      <c r="H35" s="104" t="s">
-        <v>432</v>
-      </c>
-      <c r="I35" s="93" t="s">
-        <v>267</v>
-      </c>
-      <c r="J35" s="93" t="s">
-        <v>447</v>
-      </c>
-      <c r="K35" s="94" t="s">
-        <v>267</v>
-      </c>
-      <c r="L35" s="93">
-        <v>8</v>
-      </c>
-      <c r="M35" s="94">
-        <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="N35" s="73">
-        <v>165</v>
-      </c>
-      <c r="O35" s="95" t="s">
-        <v>294</v>
-      </c>
-      <c r="P35" s="94">
-        <v>0.14319999999999999</v>
-      </c>
-      <c r="Q35" s="94">
-        <f t="shared" ref="Q35:Q36" si="24">P35*N35</f>
-        <v>23.628</v>
-      </c>
-      <c r="R35" s="96"/>
+      <c r="N35" s="72">
+        <v>45</v>
+      </c>
+      <c r="O35" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P35" s="39">
+        <v>0.1464</v>
+      </c>
+      <c r="Q35" s="92">
+        <f t="shared" si="23"/>
+        <v>6.5880000000000001</v>
+      </c>
+      <c r="R35" s="72"/>
       <c r="T35"/>
       <c r="U35"/>
       <c r="V35"/>
-    </row>
-    <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="X35"/>
+      <c r="Y35"/>
+      <c r="Z35"/>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="78" t="s">
-        <v>270</v>
-      </c>
-      <c r="D36" s="79" t="s">
-        <v>419</v>
+      <c r="B36" s="109">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="77" t="s">
+        <v>264</v>
+      </c>
+      <c r="D36" s="78" t="s">
+        <v>20</v>
       </c>
       <c r="E36" s="79" t="s">
-        <v>420</v>
-      </c>
-      <c r="F36" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="F36" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G36" s="85" t="s">
+        <v>127</v>
+      </c>
+      <c r="H36" s="96" t="s">
+        <v>194</v>
+      </c>
+      <c r="I36" s="78" t="s">
+        <v>312</v>
+      </c>
+      <c r="J36" s="78" t="s">
+        <v>313</v>
+      </c>
+      <c r="K36" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L36" s="78">
+        <v>1</v>
+      </c>
+      <c r="M36" s="72">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N36" s="72">
+        <v>30</v>
+      </c>
+      <c r="O36" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P36" s="72">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="Q36" s="72">
+        <f t="shared" ref="Q36" si="24">N36*P36</f>
+        <v>1.68</v>
+      </c>
+      <c r="R36" s="72"/>
+    </row>
+    <row r="37" spans="1:26" ht="24" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="109">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C37" s="55" t="s">
+        <v>263</v>
+      </c>
+      <c r="D37" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="G37" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="H37" s="99" t="s">
+        <v>188</v>
+      </c>
+      <c r="I37" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="K37" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L37" s="37">
+        <v>4</v>
+      </c>
+      <c r="M37" s="39">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="N37" s="39">
+        <v>100</v>
+      </c>
+      <c r="O37" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P37" s="39">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="Q37" s="39">
+        <f t="shared" ref="Q37" si="25">P37*N37</f>
+        <v>2.9499999999999997</v>
+      </c>
+      <c r="R37" s="39"/>
+    </row>
+    <row r="38" spans="1:26" ht="24" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="109">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="77" t="s">
+        <v>423</v>
+      </c>
+      <c r="D38" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>315</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="I38" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J38" s="78" t="s">
+        <v>316</v>
+      </c>
+      <c r="K38" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L38" s="78">
+        <v>1</v>
+      </c>
+      <c r="M38" s="72">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N38" s="72">
+        <v>21</v>
+      </c>
+      <c r="O38" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P38" s="72">
+        <v>0.53559999999999997</v>
+      </c>
+      <c r="Q38" s="72">
+        <f t="shared" ref="Q38" si="26">N38*P38</f>
+        <v>11.247599999999998</v>
+      </c>
+      <c r="R38" s="69"/>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="109">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C39" s="77" t="s">
         <v>421</v>
       </c>
-      <c r="G36" s="79" t="s">
+      <c r="D39" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="78" t="s">
         <v>422</v>
       </c>
-      <c r="H36" s="98" t="s">
-        <v>200</v>
-      </c>
-      <c r="I36" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J36" s="79" t="s">
-        <v>448</v>
-      </c>
-      <c r="K36" s="73" t="s">
-        <v>267</v>
-      </c>
-      <c r="L36" s="79">
+      <c r="F39" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G39" s="78" t="s">
+        <v>417</v>
+      </c>
+      <c r="H39" s="96" t="s">
+        <v>414</v>
+      </c>
+      <c r="I39" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J39" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K39" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="L39" s="78">
         <v>2</v>
       </c>
-      <c r="M36" s="94">
+      <c r="M39" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N36" s="73">
-        <v>45</v>
-      </c>
-      <c r="O36" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P36" s="39">
-        <v>0.1464</v>
-      </c>
-      <c r="Q36" s="94">
-        <f t="shared" si="24"/>
-        <v>6.5880000000000001</v>
-      </c>
-      <c r="R36" s="73"/>
-    </row>
-    <row r="37" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1"/>
-      <c r="B37" s="50">
+      <c r="N39" s="39">
+        <v>42</v>
+      </c>
+      <c r="O39" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="P39" s="39">
+        <v>2.2490000000000001</v>
+      </c>
+      <c r="Q39" s="39">
+        <f t="shared" ref="Q39" si="27">P39*N39</f>
+        <v>94.457999999999998</v>
+      </c>
+      <c r="R39" s="69"/>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="109">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C37" s="78" t="s">
-        <v>272</v>
-      </c>
-      <c r="D37" s="79" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="80" t="s">
-        <v>85</v>
-      </c>
-      <c r="F37" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="G37" s="86" t="s">
-        <v>132</v>
-      </c>
-      <c r="H37" s="98" t="s">
-        <v>201</v>
-      </c>
-      <c r="I37" s="79" t="s">
-        <v>321</v>
-      </c>
-      <c r="J37" s="79" t="s">
-        <v>322</v>
-      </c>
-      <c r="K37" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L37" s="79">
+        <v>31</v>
+      </c>
+      <c r="C40" s="77" t="s">
+        <v>266</v>
+      </c>
+      <c r="D40" s="78" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="F40" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G40" s="79" t="s">
+        <v>129</v>
+      </c>
+      <c r="H40" s="96" t="s">
+        <v>196</v>
+      </c>
+      <c r="I40" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J40" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K40" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L40" s="78">
         <v>1</v>
       </c>
-      <c r="M37" s="73">
+      <c r="M40" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N37" s="73">
-        <v>30</v>
-      </c>
-      <c r="O37" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P37" s="73">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="Q37" s="73">
-        <f t="shared" ref="Q37" si="25">N37*P37</f>
-        <v>1.68</v>
-      </c>
-      <c r="R37" s="73"/>
-    </row>
-    <row r="38" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
-      <c r="B38" s="50">
+      <c r="N40" s="72">
+        <v>21</v>
+      </c>
+      <c r="O40" s="80" t="s">
+        <v>317</v>
+      </c>
+      <c r="P40" s="72">
+        <v>1.2</v>
+      </c>
+      <c r="Q40" s="72">
+        <f t="shared" ref="Q40" si="28">N40*P40</f>
+        <v>25.2</v>
+      </c>
+      <c r="R40" s="72"/>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="109">
         <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="C38" s="56" t="s">
-        <v>271</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>263</v>
-      </c>
-      <c r="G38" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="H38" s="101" t="s">
-        <v>194</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J38" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="K38" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="L38" s="37">
-        <v>4</v>
-      </c>
-      <c r="M38" s="39">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N38" s="39">
-        <v>100</v>
-      </c>
-      <c r="O38" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P38" s="39">
-        <v>2.9499999999999998E-2</v>
-      </c>
-      <c r="Q38" s="39">
-        <f t="shared" ref="Q38" si="26">P38*N38</f>
-        <v>2.9499999999999997</v>
-      </c>
-      <c r="R38" s="39"/>
-    </row>
-    <row r="39" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1"/>
-      <c r="B39" s="50">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C39" s="78" t="s">
-        <v>435</v>
-      </c>
-      <c r="D39" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="37" t="s">
-        <v>446</v>
-      </c>
-      <c r="F39" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="G39" s="37" t="s">
-        <v>324</v>
-      </c>
-      <c r="H39" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="I39" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J39" s="79" t="s">
-        <v>325</v>
-      </c>
-      <c r="K39" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L39" s="79">
+        <v>32</v>
+      </c>
+      <c r="C41" s="55" t="s">
+        <v>266</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="G41" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="H41" s="99" t="s">
+        <v>197</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="K41" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L41" s="37">
         <v>1</v>
       </c>
-      <c r="M39" s="73">
+      <c r="M41" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N39" s="73">
-        <v>21</v>
-      </c>
-      <c r="O39" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P39" s="73">
-        <v>0.53559999999999997</v>
-      </c>
-      <c r="Q39" s="73">
-        <f t="shared" ref="Q39" si="27">N39*P39</f>
-        <v>11.247599999999998</v>
-      </c>
-      <c r="R39" s="70"/>
-    </row>
-    <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="50">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="C40" s="78" t="s">
-        <v>433</v>
-      </c>
-      <c r="D40" s="83" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="79" t="s">
-        <v>434</v>
-      </c>
-      <c r="F40" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="G40" s="79" t="s">
-        <v>429</v>
-      </c>
-      <c r="H40" s="98" t="s">
-        <v>425</v>
-      </c>
-      <c r="I40" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J40" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="K40" s="73" t="s">
-        <v>267</v>
-      </c>
-      <c r="L40" s="79">
-        <v>2</v>
-      </c>
-      <c r="M40" s="39">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N40" s="39">
-        <v>42</v>
-      </c>
-      <c r="O40" s="58" t="s">
-        <v>362</v>
-      </c>
-      <c r="P40" s="39">
-        <v>2.2490000000000001</v>
-      </c>
-      <c r="Q40" s="39">
-        <f t="shared" ref="Q40" si="28">P40*N40</f>
-        <v>94.457999999999998</v>
-      </c>
-      <c r="R40" s="70"/>
-    </row>
-    <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="50">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="78" t="s">
-        <v>274</v>
-      </c>
-      <c r="D41" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" s="80" t="s">
-        <v>87</v>
-      </c>
-      <c r="F41" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="G41" s="80" t="s">
-        <v>134</v>
-      </c>
-      <c r="H41" s="98" t="s">
-        <v>203</v>
-      </c>
-      <c r="I41" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J41" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="K41" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L41" s="79">
-        <v>1</v>
-      </c>
-      <c r="M41" s="73">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N41" s="73">
-        <v>21</v>
-      </c>
-      <c r="O41" s="81" t="s">
-        <v>326</v>
-      </c>
-      <c r="P41" s="73">
-        <v>1.2</v>
-      </c>
-      <c r="Q41" s="73">
-        <f t="shared" ref="Q41" si="29">N41*P41</f>
-        <v>25.2</v>
-      </c>
-      <c r="R41" s="73"/>
-    </row>
-    <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N41" s="39">
+        <v>30</v>
+      </c>
+      <c r="O41" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P41" s="39">
+        <v>4.65E-2</v>
+      </c>
+      <c r="Q41" s="39">
+        <f t="shared" ref="Q41:Q43" si="29">P41*N41</f>
+        <v>1.395</v>
+      </c>
+      <c r="R41" s="39"/>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="50">
+      <c r="B42" s="109">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="56" t="s">
-        <v>274</v>
+      <c r="C42" s="55" t="s">
+        <v>437</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="38" t="s">
-        <v>88</v>
+        <v>412</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>413</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="G42" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="H42" s="101" t="s">
-        <v>204</v>
+        <v>254</v>
+      </c>
+      <c r="G42" s="37">
+        <v>533980367</v>
+      </c>
+      <c r="H42" s="99" t="s">
+        <v>414</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="K42" s="38" t="s">
-        <v>267</v>
+        <v>259</v>
+      </c>
+      <c r="K42" s="39" t="s">
+        <v>259</v>
       </c>
       <c r="L42" s="37">
         <v>1</v>
@@ -4732,49 +4718,52 @@
         <v>20</v>
       </c>
       <c r="N42" s="39">
-        <v>30</v>
-      </c>
-      <c r="O42" s="58" t="s">
-        <v>294</v>
+        <v>21</v>
+      </c>
+      <c r="O42" s="57" t="s">
+        <v>353</v>
       </c>
       <c r="P42" s="39">
-        <v>4.65E-2</v>
+        <v>1.167</v>
       </c>
       <c r="Q42" s="39">
-        <f t="shared" ref="Q42:Q43" si="30">P42*N42</f>
-        <v>1.395</v>
+        <f t="shared" si="29"/>
+        <v>24.507000000000001</v>
       </c>
       <c r="R42" s="39"/>
     </row>
-    <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:26" ht="36" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="50"/>
-      <c r="C43" s="56" t="s">
-        <v>449</v>
-      </c>
-      <c r="D43" s="37" t="s">
-        <v>423</v>
-      </c>
-      <c r="E43" s="37" t="s">
-        <v>424</v>
-      </c>
-      <c r="F43" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="G43" s="37">
-        <v>533980367</v>
-      </c>
-      <c r="H43" s="101" t="s">
-        <v>425</v>
+      <c r="B43" s="109">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C43" s="55" t="s">
+        <v>437</v>
+      </c>
+      <c r="D43" s="78" t="s">
+        <v>442</v>
+      </c>
+      <c r="E43" s="78" t="s">
+        <v>444</v>
+      </c>
+      <c r="F43" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G43" s="78" t="s">
+        <v>443</v>
+      </c>
+      <c r="H43" s="78" t="s">
+        <v>445</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J43" s="37" t="s">
-        <v>267</v>
+        <v>446</v>
       </c>
       <c r="K43" s="39" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="L43" s="37">
         <v>1</v>
@@ -4784,54 +4773,54 @@
         <v>20</v>
       </c>
       <c r="N43" s="39">
-        <v>21</v>
-      </c>
-      <c r="O43" s="58" t="s">
-        <v>362</v>
+        <v>20</v>
+      </c>
+      <c r="O43" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P43" s="39">
-        <v>1.167</v>
+        <v>6.8699999999999997E-2</v>
       </c>
       <c r="Q43" s="39">
-        <f t="shared" si="30"/>
-        <v>24.507000000000001</v>
+        <f t="shared" si="29"/>
+        <v>1.3739999999999999</v>
       </c>
       <c r="R43" s="39"/>
     </row>
-    <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="50">
+      <c r="B44" s="109">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="78" t="s">
-        <v>449</v>
-      </c>
-      <c r="D44" s="83" t="s">
-        <v>406</v>
-      </c>
-      <c r="E44" s="79" t="s">
-        <v>436</v>
-      </c>
-      <c r="F44" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="G44" s="79" t="s">
-        <v>430</v>
-      </c>
-      <c r="H44" s="98" t="s">
-        <v>204</v>
-      </c>
-      <c r="I44" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J44" s="79" t="s">
-        <v>450</v>
-      </c>
-      <c r="K44" s="73" t="s">
-        <v>267</v>
-      </c>
-      <c r="L44" s="79">
+      <c r="C44" s="77" t="s">
+        <v>437</v>
+      </c>
+      <c r="D44" s="82" t="s">
+        <v>397</v>
+      </c>
+      <c r="E44" s="78" t="s">
+        <v>424</v>
+      </c>
+      <c r="F44" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G44" s="78" t="s">
+        <v>418</v>
+      </c>
+      <c r="H44" s="96" t="s">
+        <v>197</v>
+      </c>
+      <c r="I44" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J44" s="78" t="s">
+        <v>438</v>
+      </c>
+      <c r="K44" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="L44" s="78">
         <v>1</v>
       </c>
       <c r="M44" s="39">
@@ -4841,8 +4830,8 @@
       <c r="N44" s="39">
         <v>25</v>
       </c>
-      <c r="O44" s="58" t="s">
-        <v>294</v>
+      <c r="O44" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P44" s="39">
         <v>0.2044</v>
@@ -4853,93 +4842,93 @@
       </c>
       <c r="R44" s="39"/>
     </row>
-    <row r="45" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="50">
+      <c r="B45" s="109">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="78" t="s">
-        <v>271</v>
-      </c>
-      <c r="D45" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="E45" s="80" t="s">
-        <v>89</v>
-      </c>
-      <c r="F45" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="G45" s="80" t="s">
-        <v>136</v>
-      </c>
-      <c r="H45" s="98" t="s">
-        <v>194</v>
-      </c>
-      <c r="I45" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J45" s="79" t="s">
-        <v>328</v>
-      </c>
-      <c r="K45" s="80" t="s">
-        <v>239</v>
-      </c>
-      <c r="L45" s="79">
+      <c r="C45" s="77" t="s">
+        <v>263</v>
+      </c>
+      <c r="D45" s="78" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" s="79" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G45" s="79" t="s">
+        <v>131</v>
+      </c>
+      <c r="H45" s="96" t="s">
+        <v>188</v>
+      </c>
+      <c r="I45" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J45" s="78" t="s">
+        <v>319</v>
+      </c>
+      <c r="K45" s="79" t="s">
+        <v>231</v>
+      </c>
+      <c r="L45" s="78">
         <v>1</v>
       </c>
-      <c r="M45" s="73">
+      <c r="M45" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N45" s="73">
+      <c r="N45" s="72">
         <v>21</v>
       </c>
-      <c r="O45" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P45" s="73">
+      <c r="O45" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P45" s="72">
         <v>0.45629999999999998</v>
       </c>
-      <c r="Q45" s="73">
-        <f t="shared" ref="Q45" si="31">N45*P45</f>
+      <c r="Q45" s="72">
+        <f t="shared" ref="Q45" si="30">N45*P45</f>
         <v>9.5823</v>
       </c>
-      <c r="R45" s="73"/>
-    </row>
-    <row r="46" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R45" s="72"/>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="50">
+      <c r="B46" s="109">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="56" t="s">
-        <v>271</v>
+      <c r="C46" s="55" t="s">
+        <v>263</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="G46" s="38" t="s">
-        <v>387</v>
-      </c>
-      <c r="H46" s="101" t="s">
-        <v>379</v>
+        <v>378</v>
+      </c>
+      <c r="H46" s="99" t="s">
+        <v>370</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="K46" s="38" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="L46" s="37">
         <v>1</v>
@@ -4951,105 +4940,105 @@
       <c r="N46" s="39">
         <v>25</v>
       </c>
-      <c r="O46" s="58" t="s">
-        <v>294</v>
+      <c r="O46" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P46" s="39">
         <v>0.1012</v>
       </c>
       <c r="Q46" s="39">
-        <f t="shared" ref="Q46" si="32">P46*N46</f>
+        <f t="shared" ref="Q46" si="31">P46*N46</f>
         <v>2.5299999999999998</v>
       </c>
-      <c r="R46" s="69"/>
-    </row>
-    <row r="47" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R46" s="68"/>
+    </row>
+    <row r="47" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="50">
+      <c r="B47" s="109">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="78" t="s">
-        <v>275</v>
-      </c>
-      <c r="D47" s="79" t="s">
-        <v>30</v>
-      </c>
-      <c r="E47" s="80" t="s">
-        <v>90</v>
-      </c>
-      <c r="F47" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="G47" s="80" t="s">
-        <v>137</v>
-      </c>
-      <c r="H47" s="98" t="s">
-        <v>205</v>
-      </c>
-      <c r="I47" s="79" t="s">
+      <c r="C47" s="77" t="s">
         <v>267</v>
       </c>
-      <c r="J47" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="K47" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L47" s="79">
+      <c r="D47" s="78" t="s">
+        <v>28</v>
+      </c>
+      <c r="E47" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="F47" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G47" s="79" t="s">
+        <v>132</v>
+      </c>
+      <c r="H47" s="96" t="s">
+        <v>198</v>
+      </c>
+      <c r="I47" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J47" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K47" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L47" s="78">
         <v>1</v>
       </c>
-      <c r="M47" s="73">
+      <c r="M47" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N47" s="73">
+      <c r="N47" s="72">
         <v>30</v>
       </c>
-      <c r="O47" s="81" t="s">
-        <v>329</v>
-      </c>
-      <c r="P47" s="73">
+      <c r="O47" s="80" t="s">
+        <v>320</v>
+      </c>
+      <c r="P47" s="72">
         <v>0.156</v>
       </c>
-      <c r="Q47" s="73">
-        <f t="shared" ref="Q47" si="33">N47*P47</f>
+      <c r="Q47" s="72">
+        <f t="shared" ref="Q47" si="32">N47*P47</f>
         <v>4.68</v>
       </c>
-      <c r="R47" s="73"/>
-    </row>
-    <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R47" s="72"/>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="50">
+      <c r="B48" s="109">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="56" t="s">
-        <v>401</v>
+      <c r="C48" s="55" t="s">
+        <v>392</v>
       </c>
       <c r="D48" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="G48" s="38" t="s">
-        <v>404</v>
-      </c>
-      <c r="H48" s="101" t="s">
-        <v>405</v>
+        <v>395</v>
+      </c>
+      <c r="H48" s="99" t="s">
+        <v>396</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J48" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="L48" s="37">
         <v>1</v>
@@ -5061,1044 +5050,1044 @@
       <c r="N48" s="39">
         <v>20</v>
       </c>
-      <c r="O48" s="58" t="s">
-        <v>362</v>
+      <c r="O48" s="57" t="s">
+        <v>353</v>
       </c>
       <c r="P48" s="39">
         <v>0.435</v>
       </c>
       <c r="Q48" s="39">
-        <f t="shared" ref="Q48" si="34">P48*N48</f>
+        <f t="shared" ref="Q48" si="33">P48*N48</f>
         <v>8.6999999999999993</v>
       </c>
-      <c r="R48" s="70" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R48" s="69" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="50">
+      <c r="B49" s="109">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="78" t="s">
-        <v>273</v>
-      </c>
-      <c r="D49" s="79" t="s">
-        <v>31</v>
-      </c>
-      <c r="E49" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="F49" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="G49" s="80" t="s">
-        <v>138</v>
-      </c>
-      <c r="H49" s="98" t="s">
-        <v>206</v>
-      </c>
-      <c r="I49" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J49" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="K49" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L49" s="79">
+      <c r="C49" s="77" t="s">
+        <v>265</v>
+      </c>
+      <c r="D49" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="79" t="s">
+        <v>88</v>
+      </c>
+      <c r="F49" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G49" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="H49" s="96" t="s">
+        <v>199</v>
+      </c>
+      <c r="I49" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J49" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K49" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L49" s="78">
         <v>2</v>
       </c>
-      <c r="M49" s="73">
+      <c r="M49" s="72">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N49" s="73">
+      <c r="N49" s="72">
         <v>42</v>
       </c>
-      <c r="O49" s="81" t="s">
-        <v>452</v>
-      </c>
-      <c r="P49" s="73">
+      <c r="O49" s="80" t="s">
+        <v>440</v>
+      </c>
+      <c r="P49" s="72">
         <v>1.58</v>
       </c>
-      <c r="Q49" s="73">
-        <f t="shared" ref="Q49" si="35">N49*P49</f>
+      <c r="Q49" s="72">
+        <f t="shared" ref="Q49" si="34">N49*P49</f>
         <v>66.36</v>
       </c>
-      <c r="R49" s="73"/>
-    </row>
-    <row r="50" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R49" s="72"/>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="50">
+      <c r="B50" s="109">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="74" t="s">
-        <v>240</v>
-      </c>
-      <c r="D50" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="E50" s="76" t="s">
-        <v>92</v>
-      </c>
-      <c r="F50" s="75" t="s">
-        <v>262</v>
-      </c>
-      <c r="G50" s="75" t="s">
-        <v>139</v>
-      </c>
-      <c r="H50" s="105" t="s">
-        <v>267</v>
-      </c>
-      <c r="I50" s="75" t="s">
-        <v>267</v>
-      </c>
-      <c r="J50" s="75" t="s">
-        <v>267</v>
-      </c>
-      <c r="K50" s="76" t="s">
-        <v>267</v>
-      </c>
-      <c r="L50" s="75">
+      <c r="C50" s="73" t="s">
+        <v>232</v>
+      </c>
+      <c r="D50" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" s="75" t="s">
+        <v>89</v>
+      </c>
+      <c r="F50" s="74" t="s">
+        <v>254</v>
+      </c>
+      <c r="G50" s="74" t="s">
+        <v>134</v>
+      </c>
+      <c r="H50" s="103" t="s">
+        <v>259</v>
+      </c>
+      <c r="I50" s="74" t="s">
+        <v>259</v>
+      </c>
+      <c r="J50" s="74" t="s">
+        <v>259</v>
+      </c>
+      <c r="K50" s="75" t="s">
+        <v>259</v>
+      </c>
+      <c r="L50" s="74">
         <v>4</v>
       </c>
-      <c r="M50" s="59">
+      <c r="M50" s="58">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N50" s="59">
-        <f t="shared" ref="N50" si="36">M50+(M50*0.1)</f>
+      <c r="N50" s="58">
+        <f t="shared" ref="N50" si="35">M50+(M50*0.1)</f>
         <v>88</v>
       </c>
-      <c r="O50" s="59" t="s">
-        <v>267</v>
-      </c>
-      <c r="P50" s="59" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q50" s="59" t="s">
-        <v>267</v>
-      </c>
-      <c r="R50" s="59" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O50" s="58" t="s">
+        <v>259</v>
+      </c>
+      <c r="P50" s="58" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q50" s="58" t="s">
+        <v>259</v>
+      </c>
+      <c r="R50" s="58" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="50">
+      <c r="B51" s="109">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="78" t="s">
-        <v>274</v>
-      </c>
-      <c r="D51" s="79" t="s">
+      <c r="C51" s="55" t="s">
+        <v>268</v>
+      </c>
+      <c r="D51" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>425</v>
+      </c>
+      <c r="F51" s="37" t="s">
+        <v>439</v>
+      </c>
+      <c r="G51" s="37" t="s">
+        <v>322</v>
+      </c>
+      <c r="H51" s="99" t="s">
         <v>426</v>
       </c>
-      <c r="E51" s="80" t="s">
-        <v>93</v>
-      </c>
-      <c r="F51" s="79" t="s">
-        <v>140</v>
-      </c>
-      <c r="G51" s="86">
-        <v>61300211121</v>
-      </c>
-      <c r="H51" s="98" t="s">
-        <v>196</v>
-      </c>
-      <c r="I51" s="79" t="s">
-        <v>410</v>
-      </c>
-      <c r="J51" s="79" t="s">
-        <v>409</v>
-      </c>
-      <c r="K51" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L51" s="79">
+      <c r="I51" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J51" s="37" t="s">
+        <v>323</v>
+      </c>
+      <c r="K51" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L51" s="37">
+        <v>4</v>
+      </c>
+      <c r="M51" s="39">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="N51" s="39">
+        <v>85</v>
+      </c>
+      <c r="O51" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P51" s="39">
+        <v>0.21740000000000001</v>
+      </c>
+      <c r="Q51" s="39">
+        <f t="shared" ref="Q51" si="36">P51*N51</f>
+        <v>18.478999999999999</v>
+      </c>
+      <c r="R51" s="39"/>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="109">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C52" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D52" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="F52" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G52" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="H52" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="I52" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J52" s="78" t="s">
+        <v>324</v>
+      </c>
+      <c r="K52" s="79" t="s">
+        <v>233</v>
+      </c>
+      <c r="L52" s="78">
         <v>2</v>
       </c>
-      <c r="M51" s="73">
+      <c r="M52" s="72">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N51" s="73">
-        <v>50</v>
-      </c>
-      <c r="O51" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P51" s="73">
-        <v>1.47E-2</v>
-      </c>
-      <c r="Q51" s="73">
-        <f t="shared" ref="Q51" si="37">N51*P51</f>
-        <v>0.73499999999999999</v>
-      </c>
-      <c r="R51" s="73"/>
-    </row>
-    <row r="52" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="1"/>
-      <c r="B52" s="50">
+      <c r="N52" s="72">
+        <v>100</v>
+      </c>
+      <c r="O52" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P52" s="72">
+        <v>1E-3</v>
+      </c>
+      <c r="Q52" s="72">
+        <f t="shared" ref="Q52" si="37">N52*P52</f>
+        <v>0.1</v>
+      </c>
+      <c r="R52" s="72"/>
+    </row>
+    <row r="53" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+      <c r="B53" s="109">
         <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="C52" s="56" t="s">
-        <v>276</v>
-      </c>
-      <c r="D52" s="37" t="s">
-        <v>427</v>
-      </c>
-      <c r="E52" s="37" t="s">
-        <v>437</v>
-      </c>
-      <c r="F52" s="37" t="s">
-        <v>451</v>
-      </c>
-      <c r="G52" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="H52" s="101" t="s">
-        <v>438</v>
-      </c>
-      <c r="I52" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J52" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="K52" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="L52" s="37">
+        <v>44</v>
+      </c>
+      <c r="C53" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D53" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E53" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="F53" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G53" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H53" s="99" t="s">
+        <v>184</v>
+      </c>
+      <c r="I53" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J53" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="K53" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="L53" s="37">
+        <v>1</v>
+      </c>
+      <c r="M53" s="39">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N53" s="39">
+        <v>100</v>
+      </c>
+      <c r="O53" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P53" s="39">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q53" s="39">
+        <f t="shared" ref="Q53" si="38">P53*N53</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R53" s="39"/>
+    </row>
+    <row r="54" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="109">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="C54" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D54" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="E54" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G54" s="79" t="s">
+        <v>163</v>
+      </c>
+      <c r="H54" s="96" t="s">
+        <v>200</v>
+      </c>
+      <c r="I54" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J54" s="78" t="s">
+        <v>326</v>
+      </c>
+      <c r="K54" s="79" t="s">
+        <v>235</v>
+      </c>
+      <c r="L54" s="78">
+        <v>1</v>
+      </c>
+      <c r="M54" s="72">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N54" s="72">
+        <v>100</v>
+      </c>
+      <c r="O54" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P54" s="72">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="Q54" s="72">
+        <f t="shared" ref="Q54" si="39">N54*P54</f>
+        <v>0.16</v>
+      </c>
+      <c r="R54" s="72"/>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" s="1"/>
+      <c r="B55" s="109">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="C55" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D55" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="E55" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="F55" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G55" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="H55" s="99" t="s">
+        <v>184</v>
+      </c>
+      <c r="I55" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J55" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="K55" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="L55" s="37">
+        <v>2</v>
+      </c>
+      <c r="M55" s="39">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N55" s="39">
+        <v>100</v>
+      </c>
+      <c r="O55" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P55" s="39">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q55" s="39">
+        <f t="shared" ref="Q55" si="40">P55*N55</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R55" s="39"/>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+      <c r="B56" s="109">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="C56" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D56" s="78" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="F56" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G56" s="79" t="s">
+        <v>165</v>
+      </c>
+      <c r="H56" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="I56" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J56" s="78" t="s">
+        <v>328</v>
+      </c>
+      <c r="K56" s="79" t="s">
+        <v>237</v>
+      </c>
+      <c r="L56" s="78">
         <v>4</v>
       </c>
-      <c r="M52" s="39">
+      <c r="M56" s="72">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N52" s="39">
-        <v>85</v>
-      </c>
-      <c r="O52" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P52" s="39">
-        <v>0.21740000000000001</v>
-      </c>
-      <c r="Q52" s="39">
-        <f t="shared" ref="Q52" si="38">P52*N52</f>
-        <v>18.478999999999999</v>
-      </c>
-      <c r="R52" s="39"/>
-    </row>
-    <row r="53" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="50">
+      <c r="N56" s="72">
+        <v>100</v>
+      </c>
+      <c r="O56" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P56" s="72">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q56" s="72">
+        <f t="shared" ref="Q56" si="41">N56*P56</f>
+        <v>0.13</v>
+      </c>
+      <c r="R56" s="72"/>
+    </row>
+    <row r="57" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
+      <c r="B57" s="109">
         <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="C53" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="D53" s="79" t="s">
-        <v>33</v>
-      </c>
-      <c r="E53" s="80" t="s">
-        <v>94</v>
-      </c>
-      <c r="F53" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="G53" s="80" t="s">
-        <v>167</v>
-      </c>
-      <c r="H53" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="I53" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J53" s="79" t="s">
-        <v>333</v>
-      </c>
-      <c r="K53" s="80" t="s">
-        <v>241</v>
-      </c>
-      <c r="L53" s="79">
+        <v>48</v>
+      </c>
+      <c r="C57" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D57" s="37" t="s">
+        <v>403</v>
+      </c>
+      <c r="E57" s="78" t="s">
+        <v>404</v>
+      </c>
+      <c r="F57" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="G57" s="37" t="s">
+        <v>405</v>
+      </c>
+      <c r="H57" s="99" t="s">
+        <v>201</v>
+      </c>
+      <c r="I57" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J57" s="37" t="s">
+        <v>406</v>
+      </c>
+      <c r="K57" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="L57" s="37">
         <v>2</v>
       </c>
-      <c r="M53" s="73">
+      <c r="M57" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N53" s="73">
+      <c r="N57" s="39">
+        <v>45</v>
+      </c>
+      <c r="O57" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P57" s="39">
+        <v>2.9100000000000001E-2</v>
+      </c>
+      <c r="Q57" s="39">
+        <f t="shared" ref="Q57" si="42">P57*N57</f>
+        <v>1.3095000000000001</v>
+      </c>
+      <c r="R57" s="39"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="109">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="C58" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D58" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="F58" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G58" s="37" t="s">
+        <v>359</v>
+      </c>
+      <c r="H58" s="99" t="s">
+        <v>203</v>
+      </c>
+      <c r="I58" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J58" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="K58" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="L58" s="37">
+        <v>8</v>
+      </c>
+      <c r="M58" s="37">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="N58" s="72">
         <v>100</v>
       </c>
-      <c r="O53" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P53" s="73">
-        <v>1E-3</v>
-      </c>
-      <c r="Q53" s="73">
-        <f t="shared" ref="Q53" si="39">N53*P53</f>
-        <v>0.1</v>
-      </c>
-      <c r="R53" s="73"/>
-    </row>
-    <row r="54" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="50">
+      <c r="O58" s="70" t="s">
+        <v>286</v>
+      </c>
+      <c r="P58" s="37">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q58" s="37">
+        <f t="shared" ref="Q58" si="43">N58*P58</f>
+        <v>0.11</v>
+      </c>
+      <c r="R58" s="68"/>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="109">
         <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="C54" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="D54" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E54" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="F54" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="G54" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="H54" s="101" t="s">
-        <v>190</v>
-      </c>
-      <c r="I54" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J54" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="K54" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="L54" s="37">
+        <v>50</v>
+      </c>
+      <c r="C59" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D59" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E59" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="F59" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G59" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="H59" s="99" t="s">
+        <v>202</v>
+      </c>
+      <c r="I59" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J59" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="K59" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="L59" s="37">
         <v>1</v>
       </c>
-      <c r="M54" s="39">
+      <c r="M59" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N54" s="39">
-        <v>100</v>
-      </c>
-      <c r="O54" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P54" s="39">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q54" s="39">
-        <f t="shared" ref="Q54" si="40">P54*N54</f>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R54" s="39"/>
-    </row>
-    <row r="55" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="1"/>
-      <c r="B55" s="50">
+      <c r="N59" s="39">
+        <v>30</v>
+      </c>
+      <c r="O59" s="57" t="s">
+        <v>320</v>
+      </c>
+      <c r="P59" s="39">
+        <v>1.8589999999999999E-2</v>
+      </c>
+      <c r="Q59" s="39">
+        <f t="shared" ref="Q59" si="44">P59*N59</f>
+        <v>0.55769999999999997</v>
+      </c>
+      <c r="R59" s="39"/>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+      <c r="B60" s="109">
         <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="C55" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="D55" s="79" t="s">
-        <v>35</v>
-      </c>
-      <c r="E55" s="80" t="s">
-        <v>96</v>
-      </c>
-      <c r="F55" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="G55" s="80" t="s">
-        <v>169</v>
-      </c>
-      <c r="H55" s="98" t="s">
-        <v>207</v>
-      </c>
-      <c r="I55" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J55" s="79" t="s">
-        <v>335</v>
-      </c>
-      <c r="K55" s="80" t="s">
-        <v>243</v>
-      </c>
-      <c r="L55" s="79">
+        <v>51</v>
+      </c>
+      <c r="C60" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D60" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="F60" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G60" s="79" t="s">
+        <v>168</v>
+      </c>
+      <c r="H60" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="I60" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J60" s="78" t="s">
+        <v>330</v>
+      </c>
+      <c r="K60" s="79" t="s">
+        <v>240</v>
+      </c>
+      <c r="L60" s="78">
         <v>1</v>
       </c>
-      <c r="M55" s="73">
+      <c r="M60" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N55" s="73">
+      <c r="N60" s="72">
         <v>100</v>
       </c>
-      <c r="O55" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P55" s="73">
+      <c r="O60" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P60" s="72">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q60" s="72">
+        <f t="shared" ref="Q60" si="45">N60*P60</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R60" s="72"/>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61" s="1"/>
+      <c r="B61" s="109">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="C61" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D61" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E61" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="F61" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G61" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="H61" s="99" t="s">
+        <v>202</v>
+      </c>
+      <c r="I61" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J61" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="K61" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="L61" s="37">
+        <v>1</v>
+      </c>
+      <c r="M61" s="39">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N61" s="39">
+        <v>50</v>
+      </c>
+      <c r="O61" s="57" t="s">
+        <v>320</v>
+      </c>
+      <c r="P61" s="39">
+        <v>4.6699999999999997E-3</v>
+      </c>
+      <c r="Q61" s="39">
+        <f t="shared" ref="Q61" si="46">P61*N61</f>
+        <v>0.23349999999999999</v>
+      </c>
+      <c r="R61" s="39"/>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="109">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="C62" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D62" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="E62" s="79" t="s">
+        <v>99</v>
+      </c>
+      <c r="F62" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G62" s="79" t="s">
+        <v>170</v>
+      </c>
+      <c r="H62" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="I62" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J62" s="78" t="s">
+        <v>331</v>
+      </c>
+      <c r="K62" s="79" t="s">
+        <v>242</v>
+      </c>
+      <c r="L62" s="78">
+        <v>1</v>
+      </c>
+      <c r="M62" s="72">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N62" s="72">
+        <v>100</v>
+      </c>
+      <c r="O62" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P62" s="72">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q62" s="72">
+        <f t="shared" ref="Q62" si="47">N62*P62</f>
+        <v>0.12</v>
+      </c>
+      <c r="R62" s="72"/>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A63" s="1"/>
+      <c r="B63" s="109">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="C63" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D63" s="78" t="s">
+        <v>40</v>
+      </c>
+      <c r="E63" s="79" t="s">
+        <v>100</v>
+      </c>
+      <c r="F63" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G63" s="79" t="s">
+        <v>171</v>
+      </c>
+      <c r="H63" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="I63" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J63" s="78" t="s">
+        <v>332</v>
+      </c>
+      <c r="K63" s="79" t="s">
+        <v>243</v>
+      </c>
+      <c r="L63" s="78">
+        <v>1</v>
+      </c>
+      <c r="M63" s="72">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N63" s="72">
+        <v>100</v>
+      </c>
+      <c r="O63" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P63" s="72">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="Q63" s="72">
+        <f t="shared" ref="Q63" si="48">N63*P63</f>
+        <v>0.21</v>
+      </c>
+      <c r="R63" s="72"/>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="109">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="C64" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D64" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="E64" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F64" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G64" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="H64" s="99" t="s">
+        <v>184</v>
+      </c>
+      <c r="I64" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J64" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="K64" s="38" t="s">
+        <v>244</v>
+      </c>
+      <c r="L64" s="37">
+        <v>1</v>
+      </c>
+      <c r="M64" s="39">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N64" s="39">
+        <v>100</v>
+      </c>
+      <c r="O64" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P64" s="39">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q55" s="73">
-        <f t="shared" ref="Q55" si="41">N55*P55</f>
+      <c r="Q64" s="39">
+        <f t="shared" ref="Q64" si="49">P64*N64</f>
         <v>0.16</v>
       </c>
-      <c r="R55" s="73"/>
-    </row>
-    <row r="56" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="1"/>
-      <c r="B56" s="50">
+      <c r="R64" s="39"/>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="109">
         <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="C56" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="D56" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E56" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="F56" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="G56" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="H56" s="101" t="s">
-        <v>190</v>
-      </c>
-      <c r="I56" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J56" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D65" s="78" t="s">
+        <v>42</v>
+      </c>
+      <c r="E65" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="F65" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G65" s="85" t="s">
+        <v>173</v>
+      </c>
+      <c r="H65" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="I65" s="78" t="s">
+        <v>334</v>
+      </c>
+      <c r="J65" s="78" t="s">
+        <v>335</v>
+      </c>
+      <c r="K65" s="79" t="s">
+        <v>245</v>
+      </c>
+      <c r="L65" s="78">
+        <v>1</v>
+      </c>
+      <c r="M65" s="72">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N65" s="72">
+        <v>50</v>
+      </c>
+      <c r="O65" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P65" s="72">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="Q65" s="72">
+        <f t="shared" ref="Q65" si="50">N65*P65</f>
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="R65" s="72"/>
+    </row>
+    <row r="66" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="B66" s="109">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="C66" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D66" s="37" t="s">
+        <v>391</v>
+      </c>
+      <c r="E66" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="F66" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G66" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="H66" s="99" t="s">
+        <v>184</v>
+      </c>
+      <c r="I66" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J66" s="37" t="s">
         <v>336</v>
       </c>
-      <c r="K56" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="L56" s="37">
+      <c r="K66" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="L66" s="37">
         <v>2</v>
       </c>
-      <c r="M56" s="39">
+      <c r="M66" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N56" s="39">
+      <c r="N66" s="39">
         <v>100</v>
       </c>
-      <c r="O56" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P56" s="39">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q56" s="39">
-        <f t="shared" ref="Q56" si="42">P56*N56</f>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R56" s="39"/>
-    </row>
-    <row r="57" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="1"/>
-      <c r="B57" s="50">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="C57" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="D57" s="79" t="s">
-        <v>37</v>
-      </c>
-      <c r="E57" s="80" t="s">
-        <v>98</v>
-      </c>
-      <c r="F57" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="G57" s="80" t="s">
-        <v>171</v>
-      </c>
-      <c r="H57" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="I57" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J57" s="79" t="s">
-        <v>337</v>
-      </c>
-      <c r="K57" s="80" t="s">
-        <v>245</v>
-      </c>
-      <c r="L57" s="79">
-        <v>4</v>
-      </c>
-      <c r="M57" s="73">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N57" s="73">
-        <v>100</v>
-      </c>
-      <c r="O57" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P57" s="73">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q57" s="73">
-        <f t="shared" ref="Q57" si="43">N57*P57</f>
-        <v>0.13</v>
-      </c>
-      <c r="R57" s="73"/>
-    </row>
-    <row r="58" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="1"/>
-      <c r="B58" s="50">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="C58" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="D58" s="37" t="s">
-        <v>414</v>
-      </c>
-      <c r="E58" s="79" t="s">
-        <v>415</v>
-      </c>
-      <c r="F58" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="G58" s="37" t="s">
-        <v>416</v>
-      </c>
-      <c r="H58" s="101" t="s">
-        <v>208</v>
-      </c>
-      <c r="I58" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J58" s="37" t="s">
-        <v>417</v>
-      </c>
-      <c r="K58" s="38" t="s">
-        <v>418</v>
-      </c>
-      <c r="L58" s="37">
-        <v>2</v>
-      </c>
-      <c r="M58" s="39">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N58" s="39">
-        <v>45</v>
-      </c>
-      <c r="O58" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P58" s="39">
-        <v>2.9100000000000001E-2</v>
-      </c>
-      <c r="Q58" s="39">
-        <f t="shared" ref="Q58" si="44">P58*N58</f>
-        <v>1.3095000000000001</v>
-      </c>
-      <c r="R58" s="39"/>
-    </row>
-    <row r="59" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="1"/>
-      <c r="B59" s="50">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="C59" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="D59" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="E59" s="37" t="s">
-        <v>382</v>
-      </c>
-      <c r="F59" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="G59" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="H59" s="101" t="s">
-        <v>210</v>
-      </c>
-      <c r="I59" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J59" s="37" t="s">
-        <v>369</v>
-      </c>
-      <c r="K59" s="39" t="s">
-        <v>370</v>
-      </c>
-      <c r="L59" s="37">
-        <v>8</v>
-      </c>
-      <c r="M59" s="37">
-        <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="N59" s="73">
-        <v>100</v>
-      </c>
-      <c r="O59" s="71" t="s">
-        <v>294</v>
-      </c>
-      <c r="P59" s="37">
+      <c r="O66" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P66" s="39">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q59" s="37">
-        <f t="shared" ref="Q59" si="45">N59*P59</f>
+      <c r="Q66" s="39">
+        <f t="shared" ref="Q66" si="51">P66*N66</f>
         <v>0.11</v>
       </c>
-      <c r="R59" s="69"/>
-    </row>
-    <row r="60" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="1"/>
-      <c r="B60" s="50">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="C60" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="D60" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E60" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="F60" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="G60" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="H60" s="101" t="s">
-        <v>209</v>
-      </c>
-      <c r="I60" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J60" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K60" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="L60" s="37">
-        <v>1</v>
-      </c>
-      <c r="M60" s="39">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N60" s="39">
-        <v>30</v>
-      </c>
-      <c r="O60" s="58" t="s">
-        <v>329</v>
-      </c>
-      <c r="P60" s="39">
-        <v>1.8589999999999999E-2</v>
-      </c>
-      <c r="Q60" s="39">
-        <f t="shared" ref="Q60" si="46">P60*N60</f>
-        <v>0.55769999999999997</v>
-      </c>
-      <c r="R60" s="39"/>
-    </row>
-    <row r="61" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="1"/>
-      <c r="B61" s="50">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-      <c r="C61" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="D61" s="79" t="s">
-        <v>39</v>
-      </c>
-      <c r="E61" s="80" t="s">
-        <v>101</v>
-      </c>
-      <c r="F61" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="G61" s="80" t="s">
-        <v>174</v>
-      </c>
-      <c r="H61" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="I61" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J61" s="79" t="s">
-        <v>339</v>
-      </c>
-      <c r="K61" s="80" t="s">
-        <v>248</v>
-      </c>
-      <c r="L61" s="79">
-        <v>1</v>
-      </c>
-      <c r="M61" s="73">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N61" s="73">
-        <v>100</v>
-      </c>
-      <c r="O61" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P61" s="73">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q61" s="73">
-        <f t="shared" ref="Q61" si="47">N61*P61</f>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R61" s="73"/>
-    </row>
-    <row r="62" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="1"/>
-      <c r="B62" s="50">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="C62" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="D62" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="E62" s="38" t="s">
-        <v>102</v>
-      </c>
-      <c r="F62" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="G62" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="H62" s="101" t="s">
-        <v>209</v>
-      </c>
-      <c r="I62" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J62" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K62" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="L62" s="37">
-        <v>1</v>
-      </c>
-      <c r="M62" s="39">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N62" s="39">
-        <v>50</v>
-      </c>
-      <c r="O62" s="58" t="s">
-        <v>329</v>
-      </c>
-      <c r="P62" s="39">
-        <v>4.6699999999999997E-3</v>
-      </c>
-      <c r="Q62" s="39">
-        <f t="shared" ref="Q62" si="48">P62*N62</f>
-        <v>0.23349999999999999</v>
-      </c>
-      <c r="R62" s="39"/>
-    </row>
-    <row r="63" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="1"/>
-      <c r="B63" s="50">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="C63" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="D63" s="79" t="s">
-        <v>41</v>
-      </c>
-      <c r="E63" s="80" t="s">
-        <v>103</v>
-      </c>
-      <c r="F63" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="G63" s="80" t="s">
-        <v>176</v>
-      </c>
-      <c r="H63" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="I63" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J63" s="79" t="s">
-        <v>340</v>
-      </c>
-      <c r="K63" s="80" t="s">
-        <v>250</v>
-      </c>
-      <c r="L63" s="79">
-        <v>1</v>
-      </c>
-      <c r="M63" s="73">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N63" s="73">
-        <v>100</v>
-      </c>
-      <c r="O63" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P63" s="73">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q63" s="73">
-        <f t="shared" ref="Q63" si="49">N63*P63</f>
-        <v>0.12</v>
-      </c>
-      <c r="R63" s="73"/>
-    </row>
-    <row r="64" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1"/>
-      <c r="B64" s="50">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="C64" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="D64" s="79" t="s">
-        <v>42</v>
-      </c>
-      <c r="E64" s="80" t="s">
-        <v>104</v>
-      </c>
-      <c r="F64" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="G64" s="80" t="s">
-        <v>177</v>
-      </c>
-      <c r="H64" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="I64" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J64" s="79" t="s">
-        <v>341</v>
-      </c>
-      <c r="K64" s="80" t="s">
-        <v>251</v>
-      </c>
-      <c r="L64" s="79">
-        <v>1</v>
-      </c>
-      <c r="M64" s="73">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N64" s="73">
-        <v>100</v>
-      </c>
-      <c r="O64" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P64" s="73">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="Q64" s="73">
-        <f t="shared" ref="Q64" si="50">N64*P64</f>
-        <v>0.21</v>
-      </c>
-      <c r="R64" s="73"/>
-    </row>
-    <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-      <c r="B65" s="50">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="C65" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="D65" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="E65" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="F65" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="G65" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="H65" s="101" t="s">
-        <v>190</v>
-      </c>
-      <c r="I65" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J65" s="37" t="s">
-        <v>342</v>
-      </c>
-      <c r="K65" s="38" t="s">
-        <v>252</v>
-      </c>
-      <c r="L65" s="37">
-        <v>1</v>
-      </c>
-      <c r="M65" s="39">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N65" s="39">
-        <v>100</v>
-      </c>
-      <c r="O65" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P65" s="39">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="Q65" s="39">
-        <f t="shared" ref="Q65" si="51">P65*N65</f>
-        <v>0.16</v>
-      </c>
-      <c r="R65" s="39"/>
-    </row>
-    <row r="66" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="1"/>
-      <c r="B66" s="50">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
-      <c r="C66" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="D66" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="E66" s="80" t="s">
-        <v>106</v>
-      </c>
-      <c r="F66" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="G66" s="86" t="s">
-        <v>179</v>
-      </c>
-      <c r="H66" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="I66" s="79" t="s">
-        <v>343</v>
-      </c>
-      <c r="J66" s="79" t="s">
-        <v>344</v>
-      </c>
-      <c r="K66" s="80" t="s">
-        <v>253</v>
-      </c>
-      <c r="L66" s="79">
-        <v>1</v>
-      </c>
-      <c r="M66" s="73">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N66" s="73">
-        <v>50</v>
-      </c>
-      <c r="O66" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P66" s="73">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="Q66" s="73">
-        <f t="shared" ref="Q66" si="52">N66*P66</f>
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="R66" s="73"/>
-    </row>
-    <row r="67" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R66" s="39"/>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
-      <c r="B67" s="50">
+      <c r="B67" s="109">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="56" t="s">
-        <v>277</v>
+      <c r="C67" s="55" t="s">
+        <v>269</v>
       </c>
       <c r="D67" s="37" t="s">
-        <v>400</v>
+        <v>43</v>
       </c>
       <c r="E67" s="38" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G67" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="H67" s="101" t="s">
-        <v>190</v>
+        <v>175</v>
+      </c>
+      <c r="H67" s="99" t="s">
+        <v>184</v>
       </c>
       <c r="I67" s="37" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J67" s="37" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="K67" s="38" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="L67" s="37">
         <v>2</v>
@@ -6110,1174 +6099,1125 @@
       <c r="N67" s="39">
         <v>100</v>
       </c>
-      <c r="O67" s="58" t="s">
-        <v>294</v>
+      <c r="O67" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P67" s="39">
-        <v>1.1000000000000001E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="Q67" s="39">
-        <f t="shared" ref="Q67" si="53">P67*N67</f>
-        <v>0.11</v>
+        <f t="shared" ref="Q67" si="52">P67*N67</f>
+        <v>0.15</v>
       </c>
       <c r="R67" s="39"/>
     </row>
-    <row r="68" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="B68" s="50">
+      <c r="B68" s="109">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C68" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="D68" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E68" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="G68" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="H68" s="101" t="s">
-        <v>190</v>
-      </c>
-      <c r="I68" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J68" s="37" t="s">
-        <v>346</v>
-      </c>
-      <c r="K68" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="L68" s="37">
+      <c r="C68" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D68" s="82" t="s">
+        <v>358</v>
+      </c>
+      <c r="E68" s="79" t="s">
+        <v>95</v>
+      </c>
+      <c r="F68" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G68" s="79" t="s">
+        <v>166</v>
+      </c>
+      <c r="H68" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="I68" s="78"/>
+      <c r="J68" s="78" t="s">
+        <v>329</v>
+      </c>
+      <c r="K68" s="79" t="s">
+        <v>238</v>
+      </c>
+      <c r="L68" s="78">
+        <v>1</v>
+      </c>
+      <c r="M68" s="72">
+        <f>L68*20</f>
+        <v>20</v>
+      </c>
+      <c r="N68" s="72">
+        <v>100</v>
+      </c>
+      <c r="O68" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P68" s="72">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q68" s="72">
+        <f>N68*P68</f>
+        <v>0.15</v>
+      </c>
+      <c r="R68" s="68"/>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+      <c r="B69" s="109">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="C69" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D69" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E69" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="F69" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G69" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="H69" s="99" t="s">
+        <v>184</v>
+      </c>
+      <c r="I69" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J69" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="K69" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="L69" s="37">
         <v>2</v>
       </c>
-      <c r="M68" s="39">
+      <c r="M69" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N68" s="39">
+      <c r="N69" s="39">
         <v>100</v>
       </c>
-      <c r="O68" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P68" s="39">
+      <c r="O69" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P69" s="39">
         <v>1.5E-3</v>
       </c>
-      <c r="Q68" s="39">
-        <f t="shared" ref="Q68" si="54">P68*N68</f>
+      <c r="Q69" s="39">
+        <f t="shared" ref="Q69" si="53">P69*N69</f>
         <v>0.15</v>
       </c>
-      <c r="R68" s="39"/>
-    </row>
-    <row r="69" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="1"/>
-      <c r="B69" s="50">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="C69" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="D69" s="83" t="s">
-        <v>367</v>
-      </c>
-      <c r="E69" s="80" t="s">
-        <v>99</v>
-      </c>
-      <c r="F69" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="G69" s="80" t="s">
-        <v>172</v>
-      </c>
-      <c r="H69" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="I69" s="79"/>
-      <c r="J69" s="79" t="s">
-        <v>338</v>
-      </c>
-      <c r="K69" s="80" t="s">
-        <v>246</v>
-      </c>
-      <c r="L69" s="79">
-        <v>1</v>
-      </c>
-      <c r="M69" s="73">
-        <f>L69*20</f>
-        <v>20</v>
-      </c>
-      <c r="N69" s="73">
-        <v>100</v>
-      </c>
-      <c r="O69" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P69" s="73">
-        <v>1.5E-3</v>
-      </c>
-      <c r="Q69" s="73">
-        <f>N69*P69</f>
-        <v>0.15</v>
-      </c>
-      <c r="R69" s="69"/>
-    </row>
-    <row r="70" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R69" s="39"/>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="B70" s="50">
+      <c r="B70" s="109">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C70" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="D70" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E70" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="F70" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="G70" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="H70" s="101" t="s">
-        <v>190</v>
-      </c>
-      <c r="I70" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J70" s="37" t="s">
-        <v>347</v>
-      </c>
-      <c r="K70" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="L70" s="37">
-        <v>2</v>
-      </c>
-      <c r="M70" s="39">
+      <c r="C70" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D70" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="E70" s="79" t="s">
+        <v>106</v>
+      </c>
+      <c r="F70" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G70" s="79" t="s">
+        <v>177</v>
+      </c>
+      <c r="H70" s="96" t="s">
+        <v>202</v>
+      </c>
+      <c r="I70" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J70" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K70" s="79" t="s">
+        <v>249</v>
+      </c>
+      <c r="L70" s="78">
+        <v>1</v>
+      </c>
+      <c r="M70" s="72">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N70" s="39">
-        <v>100</v>
-      </c>
-      <c r="O70" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P70" s="39">
-        <v>1.5E-3</v>
-      </c>
-      <c r="Q70" s="39">
-        <f t="shared" ref="Q70" si="55">P70*N70</f>
-        <v>0.15</v>
-      </c>
-      <c r="R70" s="39"/>
-    </row>
-    <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="N70" s="72">
+        <v>25</v>
+      </c>
+      <c r="O70" s="80" t="s">
+        <v>339</v>
+      </c>
+      <c r="P70" s="72">
+        <v>8.5400000000000004E-2</v>
+      </c>
+      <c r="Q70" s="72">
+        <f t="shared" ref="Q70" si="54">N70*P70</f>
+        <v>2.1350000000000002</v>
+      </c>
+      <c r="R70" s="72"/>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
-      <c r="B71" s="50">
+      <c r="B71" s="109">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C71" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="D71" s="79" t="s">
-        <v>47</v>
-      </c>
-      <c r="E71" s="80" t="s">
-        <v>110</v>
-      </c>
-      <c r="F71" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="G71" s="80" t="s">
-        <v>183</v>
-      </c>
-      <c r="H71" s="98" t="s">
-        <v>209</v>
-      </c>
-      <c r="I71" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J71" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="K71" s="80" t="s">
-        <v>257</v>
-      </c>
-      <c r="L71" s="79">
+      <c r="C71" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D71" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E71" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="F71" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="G71" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="H71" s="99" t="s">
+        <v>203</v>
+      </c>
+      <c r="I71" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J71" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="K71" s="38" t="s">
+        <v>380</v>
+      </c>
+      <c r="L71" s="37">
         <v>1</v>
       </c>
-      <c r="M71" s="73">
-        <f t="shared" si="1"/>
+      <c r="M71" s="39">
+        <f t="shared" ref="M71:M86" si="55">L71*20</f>
         <v>20</v>
       </c>
-      <c r="N71" s="73">
-        <v>25</v>
-      </c>
-      <c r="O71" s="81" t="s">
-        <v>348</v>
-      </c>
-      <c r="P71" s="73">
-        <v>8.5400000000000004E-2</v>
-      </c>
-      <c r="Q71" s="73">
-        <f t="shared" ref="Q71" si="56">N71*P71</f>
-        <v>2.1350000000000002</v>
-      </c>
-      <c r="R71" s="73"/>
-    </row>
-    <row r="72" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N71" s="39">
+        <v>50</v>
+      </c>
+      <c r="O71" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P71" s="39">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Q71" s="39">
+        <f t="shared" ref="Q71" si="56">P71*N71</f>
+        <v>0.19</v>
+      </c>
+      <c r="R71" s="68"/>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="B72" s="50">
+      <c r="B72" s="109">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C72" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="D72" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="E72" s="38" t="s">
-        <v>377</v>
-      </c>
-      <c r="F72" s="72" t="s">
-        <v>141</v>
-      </c>
-      <c r="G72" s="38" t="s">
-        <v>390</v>
-      </c>
-      <c r="H72" s="101" t="s">
-        <v>210</v>
-      </c>
-      <c r="I72" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J72" s="37" t="s">
-        <v>378</v>
-      </c>
-      <c r="K72" s="38" t="s">
-        <v>389</v>
-      </c>
-      <c r="L72" s="37">
-        <v>1</v>
-      </c>
-      <c r="M72" s="39">
-        <f t="shared" ref="M72:M87" si="57">L72*20</f>
-        <v>20</v>
-      </c>
-      <c r="N72" s="39">
-        <v>50</v>
-      </c>
-      <c r="O72" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P72" s="39">
-        <v>3.8E-3</v>
-      </c>
-      <c r="Q72" s="39">
-        <f t="shared" ref="Q72" si="58">P72*N72</f>
-        <v>0.19</v>
-      </c>
-      <c r="R72" s="69"/>
-    </row>
-    <row r="73" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D72" s="78" t="s">
+        <v>382</v>
+      </c>
+      <c r="E72" s="79" t="s">
+        <v>109</v>
+      </c>
+      <c r="F72" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G72" s="79" t="s">
+        <v>178</v>
+      </c>
+      <c r="H72" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="I72" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J72" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="K72" s="79" t="s">
+        <v>252</v>
+      </c>
+      <c r="L72" s="78">
+        <v>6</v>
+      </c>
+      <c r="M72" s="72">
+        <f>L72*20</f>
+        <v>120</v>
+      </c>
+      <c r="N72" s="72">
+        <v>200</v>
+      </c>
+      <c r="O72" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P72" s="72">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q72" s="72">
+        <f t="shared" ref="Q72" si="57">N72*P72</f>
+        <v>0.24</v>
+      </c>
+      <c r="R72" s="68"/>
+    </row>
+    <row r="73" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
-      <c r="B73" s="50">
+      <c r="B73" s="109">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="D73" s="79" t="s">
-        <v>391</v>
-      </c>
-      <c r="E73" s="80" t="s">
-        <v>113</v>
-      </c>
-      <c r="F73" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="G73" s="80" t="s">
-        <v>184</v>
-      </c>
-      <c r="H73" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="I73" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J73" s="79" t="s">
-        <v>351</v>
-      </c>
-      <c r="K73" s="80" t="s">
-        <v>260</v>
-      </c>
-      <c r="L73" s="79">
-        <v>6</v>
-      </c>
-      <c r="M73" s="73">
-        <f>L73*20</f>
-        <v>120</v>
-      </c>
-      <c r="N73" s="73">
-        <v>200</v>
-      </c>
-      <c r="O73" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P73" s="73">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q73" s="73">
-        <f t="shared" ref="Q73" si="59">N73*P73</f>
-        <v>0.24</v>
-      </c>
-      <c r="R73" s="69"/>
-    </row>
-    <row r="74" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C73" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D73" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="E73" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="F73" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G73" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="H73" s="99" t="s">
+        <v>203</v>
+      </c>
+      <c r="I73" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J73" s="37" t="s">
+        <v>340</v>
+      </c>
+      <c r="K73" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="L73" s="37">
+        <v>1</v>
+      </c>
+      <c r="M73" s="39">
+        <f t="shared" si="55"/>
+        <v>20</v>
+      </c>
+      <c r="N73" s="39">
+        <v>100</v>
+      </c>
+      <c r="O73" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P73" s="39">
+        <v>1E-3</v>
+      </c>
+      <c r="Q73" s="39">
+        <f t="shared" ref="Q73" si="58">P73*N73</f>
+        <v>0.1</v>
+      </c>
+      <c r="R73" s="39"/>
+    </row>
+    <row r="74" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="B74" s="50">
+      <c r="B74" s="109">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="C74" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="D74" s="37" t="s">
+      <c r="C74" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D74" s="78" t="s">
+        <v>48</v>
+      </c>
+      <c r="E74" s="79" t="s">
+        <v>108</v>
+      </c>
+      <c r="F74" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G74" s="79" t="s">
+        <v>275</v>
+      </c>
+      <c r="H74" s="96" t="s">
+        <v>204</v>
+      </c>
+      <c r="I74" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J74" s="78" t="s">
+        <v>341</v>
+      </c>
+      <c r="K74" s="79" t="s">
+        <v>251</v>
+      </c>
+      <c r="L74" s="78">
+        <v>1</v>
+      </c>
+      <c r="M74" s="72">
+        <f t="shared" si="55"/>
+        <v>20</v>
+      </c>
+      <c r="N74" s="72">
+        <v>50</v>
+      </c>
+      <c r="O74" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P74" s="72">
+        <v>4.3E-3</v>
+      </c>
+      <c r="Q74" s="72">
+        <f t="shared" ref="Q74" si="59">N74*P74</f>
+        <v>0.215</v>
+      </c>
+      <c r="R74" s="72"/>
+    </row>
+    <row r="75" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A75" s="1"/>
+      <c r="B75" s="109">
+        <f t="shared" ref="B75:B86" si="60">ROW(B75) - ROW($B$9)</f>
+        <v>66</v>
+      </c>
+      <c r="C75" s="77" t="s">
+        <v>271</v>
+      </c>
+      <c r="D75" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="E74" s="38" t="s">
+      <c r="E75" s="79" t="s">
+        <v>110</v>
+      </c>
+      <c r="F75" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G75" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="H75" s="96" t="s">
+        <v>205</v>
+      </c>
+      <c r="I75" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J75" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K75" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L75" s="78">
+        <v>1</v>
+      </c>
+      <c r="M75" s="72">
+        <f t="shared" si="55"/>
+        <v>20</v>
+      </c>
+      <c r="N75" s="72">
+        <f t="shared" ref="N75" si="61">M75+(M75*0.1)</f>
+        <v>22</v>
+      </c>
+      <c r="O75" s="80" t="s">
+        <v>400</v>
+      </c>
+      <c r="P75" s="72">
+        <v>1.42</v>
+      </c>
+      <c r="Q75" s="72">
+        <v>1.42</v>
+      </c>
+      <c r="R75" s="72"/>
+    </row>
+    <row r="76" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A76" s="1"/>
+      <c r="B76" s="109">
+        <f t="shared" si="60"/>
+        <v>67</v>
+      </c>
+      <c r="C76" s="55" t="s">
+        <v>272</v>
+      </c>
+      <c r="D76" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E76" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="F74" s="37" t="s">
+      <c r="F76" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="G76" s="38">
+        <v>750314597</v>
+      </c>
+      <c r="H76" s="99" t="s">
+        <v>206</v>
+      </c>
+      <c r="I76" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J76" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="K76" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L76" s="37">
+        <v>1</v>
+      </c>
+      <c r="M76" s="39">
+        <f t="shared" si="55"/>
+        <v>20</v>
+      </c>
+      <c r="N76" s="39">
+        <v>21</v>
+      </c>
+      <c r="O76" s="57" t="s">
+        <v>317</v>
+      </c>
+      <c r="P76" s="39">
+        <v>3.81</v>
+      </c>
+      <c r="Q76" s="39">
+        <f t="shared" ref="Q76" si="62">P76*N76</f>
+        <v>80.010000000000005</v>
+      </c>
+      <c r="R76" s="39"/>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A77" s="1"/>
+      <c r="B77" s="109">
+        <f t="shared" si="60"/>
+        <v>68</v>
+      </c>
+      <c r="C77" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="D77" s="78" t="s">
+        <v>51</v>
+      </c>
+      <c r="E77" s="79" t="s">
+        <v>112</v>
+      </c>
+      <c r="F77" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G77" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="H77" s="96" t="s">
+        <v>207</v>
+      </c>
+      <c r="I77" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J77" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K77" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L77" s="78">
+        <v>1</v>
+      </c>
+      <c r="M77" s="72">
+        <f t="shared" si="55"/>
+        <v>20</v>
+      </c>
+      <c r="N77" s="72">
+        <v>21</v>
+      </c>
+      <c r="O77" s="80" t="s">
+        <v>343</v>
+      </c>
+      <c r="P77" s="72">
+        <v>2.48</v>
+      </c>
+      <c r="Q77" s="72">
+        <f t="shared" ref="Q77" si="63">N77*P77</f>
+        <v>52.08</v>
+      </c>
+      <c r="R77" s="72"/>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A78" s="1"/>
+      <c r="B78" s="109">
+        <f t="shared" si="60"/>
+        <v>69</v>
+      </c>
+      <c r="C78" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="D78" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="E78" s="78" t="s">
+        <v>427</v>
+      </c>
+      <c r="F78" s="78" t="s">
+        <v>428</v>
+      </c>
+      <c r="G78" s="78" t="s">
+        <v>344</v>
+      </c>
+      <c r="H78" s="96" t="s">
+        <v>207</v>
+      </c>
+      <c r="I78" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J78" s="37" t="s">
+        <v>345</v>
+      </c>
+      <c r="K78" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L78" s="37">
+        <v>1</v>
+      </c>
+      <c r="M78" s="39">
+        <f t="shared" si="55"/>
+        <v>20</v>
+      </c>
+      <c r="N78" s="39">
+        <v>25</v>
+      </c>
+      <c r="O78" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P78" s="39">
+        <v>0.34410000000000002</v>
+      </c>
+      <c r="Q78" s="39">
+        <f t="shared" ref="Q78" si="64">P78*N78</f>
+        <v>8.6025000000000009</v>
+      </c>
+      <c r="R78" s="69"/>
+    </row>
+    <row r="79" spans="1:18" ht="36" x14ac:dyDescent="0.25">
+      <c r="A79" s="1"/>
+      <c r="B79" s="109">
+        <f t="shared" si="60"/>
+        <v>70</v>
+      </c>
+      <c r="C79" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="D79" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="E79" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="F79" s="37" t="s">
+        <v>430</v>
+      </c>
+      <c r="G79" s="37" t="s">
+        <v>346</v>
+      </c>
+      <c r="H79" s="99" t="s">
+        <v>431</v>
+      </c>
+      <c r="I79" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J79" s="78" t="s">
+        <v>347</v>
+      </c>
+      <c r="K79" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L79" s="78">
+        <v>1</v>
+      </c>
+      <c r="M79" s="72">
+        <f t="shared" si="55"/>
+        <v>20</v>
+      </c>
+      <c r="N79" s="72">
+        <v>21</v>
+      </c>
+      <c r="O79" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P79" s="72">
+        <v>0.30709999999999998</v>
+      </c>
+      <c r="Q79" s="72">
+        <f t="shared" ref="Q79" si="65">N79*P79</f>
+        <v>6.4490999999999996</v>
+      </c>
+      <c r="R79" s="69"/>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A80" s="1"/>
+      <c r="B80" s="109">
+        <f t="shared" si="60"/>
+        <v>71</v>
+      </c>
+      <c r="C80" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="D80" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E80" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="F80" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="G80" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="H80" s="99" t="s">
+        <v>207</v>
+      </c>
+      <c r="I80" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J80" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="K80" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L80" s="37">
+        <v>1</v>
+      </c>
+      <c r="M80" s="39">
+        <f t="shared" si="55"/>
+        <v>20</v>
+      </c>
+      <c r="N80" s="39">
+        <v>21</v>
+      </c>
+      <c r="O80" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="P80" s="39">
+        <v>3.637</v>
+      </c>
+      <c r="Q80" s="39">
+        <f t="shared" ref="Q80" si="66">P80*N80</f>
+        <v>76.376999999999995</v>
+      </c>
+      <c r="R80" s="39"/>
+    </row>
+    <row r="81" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A81" s="1"/>
+      <c r="B81" s="109">
+        <f t="shared" si="60"/>
+        <v>72</v>
+      </c>
+      <c r="C81" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="D81" s="78" t="s">
+        <v>55</v>
+      </c>
+      <c r="E81" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="F81" s="78" t="s">
+        <v>140</v>
+      </c>
+      <c r="G81" s="79" t="s">
+        <v>179</v>
+      </c>
+      <c r="H81" s="96" t="s">
+        <v>207</v>
+      </c>
+      <c r="I81" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J81" s="78" t="s">
+        <v>348</v>
+      </c>
+      <c r="K81" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L81" s="78">
+        <v>1</v>
+      </c>
+      <c r="M81" s="72">
+        <f t="shared" si="55"/>
+        <v>20</v>
+      </c>
+      <c r="N81" s="72">
+        <v>25</v>
+      </c>
+      <c r="O81" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P81" s="72">
+        <v>0.3463</v>
+      </c>
+      <c r="Q81" s="72">
+        <f t="shared" ref="Q81" si="67">N81*P81</f>
+        <v>8.6575000000000006</v>
+      </c>
+      <c r="R81" s="72"/>
+    </row>
+    <row r="82" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A82" s="1"/>
+      <c r="B82" s="109">
+        <f t="shared" si="60"/>
+        <v>73</v>
+      </c>
+      <c r="C82" s="63" t="s">
+        <v>273</v>
+      </c>
+      <c r="D82" s="64" t="s">
+        <v>56</v>
+      </c>
+      <c r="E82" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="F82" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="G74" s="38" t="s">
-        <v>282</v>
-      </c>
-      <c r="H74" s="101" t="s">
-        <v>210</v>
-      </c>
-      <c r="I74" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J74" s="37" t="s">
+      <c r="G82" s="65" t="s">
+        <v>180</v>
+      </c>
+      <c r="H82" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="I82" s="64" t="s">
+        <v>259</v>
+      </c>
+      <c r="J82" s="64" t="s">
         <v>349</v>
       </c>
-      <c r="K74" s="38" t="s">
+      <c r="K82" s="65" t="s">
+        <v>259</v>
+      </c>
+      <c r="L82" s="64">
+        <v>1</v>
+      </c>
+      <c r="M82" s="66">
+        <f t="shared" si="55"/>
+        <v>20</v>
+      </c>
+      <c r="N82" s="66">
+        <v>21</v>
+      </c>
+      <c r="O82" s="67" t="s">
+        <v>286</v>
+      </c>
+      <c r="P82" s="66">
+        <v>7.4638</v>
+      </c>
+      <c r="Q82" s="66">
+        <f t="shared" ref="Q82" si="68">P82*N82</f>
+        <v>156.7398</v>
+      </c>
+      <c r="R82" s="66" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A83" s="1"/>
+      <c r="B83" s="109">
+        <f t="shared" si="60"/>
+        <v>74</v>
+      </c>
+      <c r="C83" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="D83" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="E83" s="79" t="s">
+        <v>116</v>
+      </c>
+      <c r="F83" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="G83" s="79" t="s">
+        <v>181</v>
+      </c>
+      <c r="H83" s="96" t="s">
+        <v>209</v>
+      </c>
+      <c r="I83" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J83" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K83" s="83" t="s">
+        <v>259</v>
+      </c>
+      <c r="L83" s="78">
+        <v>1</v>
+      </c>
+      <c r="M83" s="72">
+        <f t="shared" si="55"/>
+        <v>20</v>
+      </c>
+      <c r="N83" s="72">
+        <v>21</v>
+      </c>
+      <c r="O83" s="80" t="s">
+        <v>343</v>
+      </c>
+      <c r="P83" s="72">
+        <v>2.6459999999999999</v>
+      </c>
+      <c r="Q83" s="72">
+        <f t="shared" ref="Q83" si="69">N83*P83</f>
+        <v>55.565999999999995</v>
+      </c>
+      <c r="R83" s="72"/>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84" s="1"/>
+      <c r="B84" s="109">
+        <f t="shared" si="60"/>
+        <v>75</v>
+      </c>
+      <c r="C84" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="D84" s="82" t="s">
+        <v>383</v>
+      </c>
+      <c r="E84" s="78" t="s">
+        <v>432</v>
+      </c>
+      <c r="F84" s="78" t="s">
+        <v>140</v>
+      </c>
+      <c r="G84" s="78" t="s">
+        <v>350</v>
+      </c>
+      <c r="H84" s="96" t="s">
+        <v>207</v>
+      </c>
+      <c r="I84" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J84" s="37" t="s">
+        <v>351</v>
+      </c>
+      <c r="K84" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L84" s="71">
+        <v>2</v>
+      </c>
+      <c r="M84" s="39">
+        <f t="shared" si="55"/>
+        <v>40</v>
+      </c>
+      <c r="N84" s="39">
+        <v>41</v>
+      </c>
+      <c r="O84" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P84" s="39">
+        <v>1.1423000000000001</v>
+      </c>
+      <c r="Q84" s="39">
+        <f t="shared" ref="Q84" si="70">P84*N84</f>
+        <v>46.834300000000006</v>
+      </c>
+      <c r="R84" s="69"/>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A85" s="1"/>
+      <c r="B85" s="109">
+        <f t="shared" si="60"/>
+        <v>76</v>
+      </c>
+      <c r="C85" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="D85" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E85" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="F85" s="37" t="s">
         <v>258</v>
       </c>
-      <c r="L74" s="37">
+      <c r="G85" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="H85" s="99" t="s">
+        <v>207</v>
+      </c>
+      <c r="I85" s="97" t="s">
+        <v>259</v>
+      </c>
+      <c r="J85" s="97" t="s">
+        <v>354</v>
+      </c>
+      <c r="K85" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L85" s="37">
         <v>1</v>
       </c>
-      <c r="M74" s="39">
-        <f t="shared" si="57"/>
+      <c r="M85" s="39">
+        <f>L85*20</f>
         <v>20</v>
       </c>
-      <c r="N74" s="39">
-        <v>100</v>
-      </c>
-      <c r="O74" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P74" s="39">
-        <v>1E-3</v>
-      </c>
-      <c r="Q74" s="39">
-        <f t="shared" ref="Q74" si="60">P74*N74</f>
-        <v>0.1</v>
-      </c>
-      <c r="R74" s="39"/>
-    </row>
-    <row r="75" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="1"/>
-      <c r="B75" s="50">
-        <f t="shared" ref="B75:B87" si="61">ROW(B75) - ROW($B$9)</f>
-        <v>66</v>
-      </c>
-      <c r="C75" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="D75" s="79" t="s">
-        <v>50</v>
-      </c>
-      <c r="E75" s="80" t="s">
-        <v>112</v>
-      </c>
-      <c r="F75" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="G75" s="80" t="s">
-        <v>283</v>
-      </c>
-      <c r="H75" s="98" t="s">
-        <v>211</v>
-      </c>
-      <c r="I75" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J75" s="79" t="s">
-        <v>350</v>
-      </c>
-      <c r="K75" s="80" t="s">
-        <v>259</v>
-      </c>
-      <c r="L75" s="79">
-        <v>1</v>
-      </c>
-      <c r="M75" s="73">
-        <f t="shared" si="57"/>
-        <v>20</v>
-      </c>
-      <c r="N75" s="73">
-        <v>50</v>
-      </c>
-      <c r="O75" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P75" s="73">
-        <v>4.3E-3</v>
-      </c>
-      <c r="Q75" s="73">
-        <f t="shared" ref="Q75" si="62">N75*P75</f>
-        <v>0.215</v>
-      </c>
-      <c r="R75" s="73"/>
-    </row>
-    <row r="76" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="1"/>
-      <c r="B76" s="50">
-        <f t="shared" si="61"/>
-        <v>67</v>
-      </c>
-      <c r="C76" s="78" t="s">
-        <v>279</v>
-      </c>
-      <c r="D76" s="79" t="s">
-        <v>51</v>
-      </c>
-      <c r="E76" s="80" t="s">
-        <v>114</v>
-      </c>
-      <c r="F76" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="G76" s="79" t="s">
-        <v>143</v>
-      </c>
-      <c r="H76" s="98" t="s">
-        <v>212</v>
-      </c>
-      <c r="I76" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J76" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="K76" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L76" s="79">
-        <v>1</v>
-      </c>
-      <c r="M76" s="73">
-        <f t="shared" si="57"/>
-        <v>20</v>
-      </c>
-      <c r="N76" s="73">
-        <f t="shared" ref="N76" si="63">M76+(M76*0.1)</f>
-        <v>22</v>
-      </c>
-      <c r="O76" s="81" t="s">
-        <v>411</v>
-      </c>
-      <c r="P76" s="73">
-        <v>1.42</v>
-      </c>
-      <c r="Q76" s="73">
-        <v>1.42</v>
-      </c>
-      <c r="R76" s="73"/>
-    </row>
-    <row r="77" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="1"/>
-      <c r="B77" s="50">
-        <f t="shared" si="61"/>
-        <v>68</v>
-      </c>
-      <c r="C77" s="56" t="s">
-        <v>280</v>
-      </c>
-      <c r="D77" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E77" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="F77" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="G77" s="38">
-        <v>750314597</v>
-      </c>
-      <c r="H77" s="101" t="s">
-        <v>213</v>
-      </c>
-      <c r="I77" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J77" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K77" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="L77" s="37">
-        <v>1</v>
-      </c>
-      <c r="M77" s="39">
-        <f t="shared" si="57"/>
-        <v>20</v>
-      </c>
-      <c r="N77" s="39">
+      <c r="N85" s="39">
         <v>21</v>
       </c>
-      <c r="O77" s="58" t="s">
-        <v>326</v>
-      </c>
-      <c r="P77" s="39">
-        <v>3.81</v>
-      </c>
-      <c r="Q77" s="39">
-        <f t="shared" ref="Q77" si="64">P77*N77</f>
-        <v>80.010000000000005</v>
-      </c>
-      <c r="R77" s="39"/>
-    </row>
-    <row r="78" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="1"/>
-      <c r="B78" s="50">
-        <f t="shared" si="61"/>
-        <v>69</v>
-      </c>
-      <c r="C78" s="78" t="s">
-        <v>281</v>
-      </c>
-      <c r="D78" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="E78" s="80" t="s">
-        <v>116</v>
-      </c>
-      <c r="F78" s="79" t="s">
-        <v>262</v>
-      </c>
-      <c r="G78" s="80" t="s">
-        <v>144</v>
-      </c>
-      <c r="H78" s="98" t="s">
-        <v>214</v>
-      </c>
-      <c r="I78" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J78" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="K78" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L78" s="79">
-        <v>1</v>
-      </c>
-      <c r="M78" s="73">
-        <f t="shared" si="57"/>
-        <v>20</v>
-      </c>
-      <c r="N78" s="73">
-        <v>21</v>
-      </c>
-      <c r="O78" s="81" t="s">
-        <v>352</v>
-      </c>
-      <c r="P78" s="73">
-        <v>2.48</v>
-      </c>
-      <c r="Q78" s="73">
-        <f t="shared" ref="Q78" si="65">N78*P78</f>
-        <v>52.08</v>
-      </c>
-      <c r="R78" s="73"/>
-    </row>
-    <row r="79" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="1"/>
-      <c r="B79" s="50">
-        <f t="shared" si="61"/>
-        <v>70</v>
-      </c>
-      <c r="C79" s="56" t="s">
-        <v>281</v>
-      </c>
-      <c r="D79" s="83" t="s">
-        <v>54</v>
-      </c>
-      <c r="E79" s="79" t="s">
-        <v>439</v>
-      </c>
-      <c r="F79" s="79" t="s">
-        <v>440</v>
-      </c>
-      <c r="G79" s="79" t="s">
-        <v>353</v>
-      </c>
-      <c r="H79" s="98" t="s">
-        <v>214</v>
-      </c>
-      <c r="I79" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J79" s="37" t="s">
-        <v>354</v>
-      </c>
-      <c r="K79" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="L79" s="37">
-        <v>1</v>
-      </c>
-      <c r="M79" s="39">
-        <f t="shared" si="57"/>
-        <v>20</v>
-      </c>
-      <c r="N79" s="39">
-        <v>25</v>
-      </c>
-      <c r="O79" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P79" s="39">
-        <v>0.34410000000000002</v>
-      </c>
-      <c r="Q79" s="39">
-        <f t="shared" ref="Q79" si="66">P79*N79</f>
-        <v>8.6025000000000009</v>
-      </c>
-      <c r="R79" s="70"/>
-    </row>
-    <row r="80" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="1"/>
-      <c r="B80" s="50">
-        <f t="shared" si="61"/>
-        <v>71</v>
-      </c>
-      <c r="C80" s="78" t="s">
-        <v>281</v>
-      </c>
-      <c r="D80" s="72" t="s">
-        <v>55</v>
-      </c>
-      <c r="E80" s="37" t="s">
-        <v>441</v>
-      </c>
-      <c r="F80" s="37" t="s">
-        <v>442</v>
-      </c>
-      <c r="G80" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="H80" s="101" t="s">
-        <v>443</v>
-      </c>
-      <c r="I80" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J80" s="79" t="s">
-        <v>356</v>
-      </c>
-      <c r="K80" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L80" s="79">
-        <v>1</v>
-      </c>
-      <c r="M80" s="73">
-        <f t="shared" si="57"/>
-        <v>20</v>
-      </c>
-      <c r="N80" s="73">
-        <v>21</v>
-      </c>
-      <c r="O80" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P80" s="73">
-        <v>0.30709999999999998</v>
-      </c>
-      <c r="Q80" s="73">
-        <f t="shared" ref="Q80" si="67">N80*P80</f>
-        <v>6.4490999999999996</v>
-      </c>
-      <c r="R80" s="70"/>
-    </row>
-    <row r="81" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="1"/>
-      <c r="B81" s="50">
-        <f t="shared" si="61"/>
-        <v>72</v>
-      </c>
-      <c r="C81" s="56" t="s">
-        <v>281</v>
-      </c>
-      <c r="D81" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="E81" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="F81" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="G81" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="H81" s="101" t="s">
-        <v>214</v>
-      </c>
-      <c r="I81" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J81" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K81" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="L81" s="37">
-        <v>1</v>
-      </c>
-      <c r="M81" s="39">
-        <f t="shared" si="57"/>
-        <v>20</v>
-      </c>
-      <c r="N81" s="39">
-        <v>21</v>
-      </c>
-      <c r="O81" s="58" t="s">
-        <v>352</v>
-      </c>
-      <c r="P81" s="39">
-        <v>3.637</v>
-      </c>
-      <c r="Q81" s="39">
-        <f t="shared" ref="Q81" si="68">P81*N81</f>
-        <v>76.376999999999995</v>
-      </c>
-      <c r="R81" s="39"/>
-    </row>
-    <row r="82" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="1"/>
-      <c r="B82" s="50">
-        <f t="shared" si="61"/>
-        <v>73</v>
-      </c>
-      <c r="C82" s="78" t="s">
-        <v>281</v>
-      </c>
-      <c r="D82" s="79" t="s">
-        <v>57</v>
-      </c>
-      <c r="E82" s="80" t="s">
-        <v>118</v>
-      </c>
-      <c r="F82" s="79" t="s">
-        <v>146</v>
-      </c>
-      <c r="G82" s="80" t="s">
-        <v>185</v>
-      </c>
-      <c r="H82" s="98" t="s">
-        <v>214</v>
-      </c>
-      <c r="I82" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J82" s="79" t="s">
-        <v>357</v>
-      </c>
-      <c r="K82" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L82" s="79">
-        <v>1</v>
-      </c>
-      <c r="M82" s="73">
-        <f t="shared" si="57"/>
-        <v>20</v>
-      </c>
-      <c r="N82" s="73">
-        <v>25</v>
-      </c>
-      <c r="O82" s="81" t="s">
-        <v>294</v>
-      </c>
-      <c r="P82" s="73">
-        <v>0.3463</v>
-      </c>
-      <c r="Q82" s="73">
-        <f t="shared" ref="Q82" si="69">N82*P82</f>
-        <v>8.6575000000000006</v>
-      </c>
-      <c r="R82" s="73"/>
-    </row>
-    <row r="83" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1"/>
-      <c r="B83" s="50">
-        <f t="shared" si="61"/>
-        <v>74</v>
-      </c>
-      <c r="C83" s="64" t="s">
-        <v>281</v>
-      </c>
-      <c r="D83" s="65" t="s">
-        <v>58</v>
-      </c>
-      <c r="E83" s="66" t="s">
-        <v>119</v>
-      </c>
-      <c r="F83" s="65" t="s">
-        <v>147</v>
-      </c>
-      <c r="G83" s="66" t="s">
-        <v>186</v>
-      </c>
-      <c r="H83" s="106" t="s">
-        <v>215</v>
-      </c>
-      <c r="I83" s="65" t="s">
-        <v>267</v>
-      </c>
-      <c r="J83" s="65" t="s">
-        <v>358</v>
-      </c>
-      <c r="K83" s="66" t="s">
-        <v>267</v>
-      </c>
-      <c r="L83" s="65">
-        <v>1</v>
-      </c>
-      <c r="M83" s="67">
-        <f t="shared" si="57"/>
-        <v>20</v>
-      </c>
-      <c r="N83" s="67">
-        <v>21</v>
-      </c>
-      <c r="O83" s="68" t="s">
-        <v>294</v>
-      </c>
-      <c r="P83" s="67">
-        <v>7.4638</v>
-      </c>
-      <c r="Q83" s="67">
-        <f t="shared" ref="Q83" si="70">P83*N83</f>
-        <v>156.7398</v>
-      </c>
-      <c r="R83" s="67" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1"/>
-      <c r="B84" s="50">
-        <f t="shared" si="61"/>
-        <v>75</v>
-      </c>
-      <c r="C84" s="78" t="s">
-        <v>281</v>
-      </c>
-      <c r="D84" s="79" t="s">
-        <v>59</v>
-      </c>
-      <c r="E84" s="80" t="s">
-        <v>120</v>
-      </c>
-      <c r="F84" s="79" t="s">
-        <v>148</v>
-      </c>
-      <c r="G84" s="80" t="s">
-        <v>187</v>
-      </c>
-      <c r="H84" s="98" t="s">
-        <v>216</v>
-      </c>
-      <c r="I84" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J84" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="K84" s="84" t="s">
-        <v>267</v>
-      </c>
-      <c r="L84" s="79">
-        <v>1</v>
-      </c>
-      <c r="M84" s="73">
-        <f t="shared" si="57"/>
-        <v>20</v>
-      </c>
-      <c r="N84" s="73">
-        <v>21</v>
-      </c>
-      <c r="O84" s="81" t="s">
-        <v>352</v>
-      </c>
-      <c r="P84" s="73">
-        <v>2.6459999999999999</v>
-      </c>
-      <c r="Q84" s="73">
-        <f t="shared" ref="Q84" si="71">N84*P84</f>
-        <v>55.565999999999995</v>
-      </c>
-      <c r="R84" s="73"/>
-    </row>
-    <row r="85" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="1"/>
-      <c r="B85" s="50">
-        <f t="shared" si="61"/>
-        <v>76</v>
-      </c>
-      <c r="C85" s="56" t="s">
-        <v>281</v>
-      </c>
-      <c r="D85" s="83" t="s">
-        <v>392</v>
-      </c>
-      <c r="E85" s="79" t="s">
-        <v>444</v>
-      </c>
-      <c r="F85" s="79" t="s">
-        <v>146</v>
-      </c>
-      <c r="G85" s="79" t="s">
-        <v>359</v>
-      </c>
-      <c r="H85" s="98" t="s">
-        <v>214</v>
-      </c>
-      <c r="I85" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J85" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="K85" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="L85" s="72">
-        <v>2</v>
-      </c>
-      <c r="M85" s="39">
-        <f t="shared" si="57"/>
-        <v>40</v>
-      </c>
-      <c r="N85" s="39">
-        <v>41</v>
-      </c>
-      <c r="O85" s="58" t="s">
-        <v>294</v>
+      <c r="O85" s="57" t="s">
+        <v>286</v>
       </c>
       <c r="P85" s="39">
-        <v>1.1423000000000001</v>
+        <v>0.39140000000000003</v>
       </c>
       <c r="Q85" s="39">
-        <f t="shared" ref="Q85" si="72">P85*N85</f>
-        <v>46.834300000000006</v>
-      </c>
-      <c r="R85" s="70"/>
+        <f t="shared" ref="Q85" si="71">P85*N85</f>
+        <v>8.2194000000000003</v>
+      </c>
+      <c r="R85" s="39"/>
     </row>
     <row r="86" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
-      <c r="B86" s="50">
-        <f t="shared" si="61"/>
+      <c r="B86" s="109">
+        <f t="shared" si="60"/>
         <v>77</v>
       </c>
-      <c r="C86" s="56" t="s">
-        <v>281</v>
-      </c>
-      <c r="D86" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="E86" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="F86" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="G86" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="H86" s="101" t="s">
-        <v>214</v>
-      </c>
-      <c r="I86" s="99" t="s">
-        <v>267</v>
-      </c>
-      <c r="J86" s="99" t="s">
-        <v>363</v>
-      </c>
-      <c r="K86" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="L86" s="37">
+      <c r="C86" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="D86" s="82" t="s">
+        <v>384</v>
+      </c>
+      <c r="E86" s="78" t="s">
+        <v>433</v>
+      </c>
+      <c r="F86" s="78" t="s">
+        <v>257</v>
+      </c>
+      <c r="G86" s="78" t="s">
+        <v>352</v>
+      </c>
+      <c r="H86" s="96" t="s">
+        <v>207</v>
+      </c>
+      <c r="I86" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J86" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K86" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L86" s="78">
         <v>1</v>
       </c>
-      <c r="M86" s="39">
-        <f>L86*20</f>
+      <c r="M86" s="72">
+        <f t="shared" si="55"/>
         <v>20</v>
       </c>
-      <c r="N86" s="39">
+      <c r="N86" s="72">
         <v>21</v>
       </c>
-      <c r="O86" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="P86" s="39">
-        <v>0.39140000000000003</v>
-      </c>
-      <c r="Q86" s="39">
-        <f t="shared" ref="Q86" si="73">P86*N86</f>
-        <v>8.2194000000000003</v>
-      </c>
-      <c r="R86" s="39"/>
-    </row>
-    <row r="87" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O86" s="80" t="s">
+        <v>353</v>
+      </c>
+      <c r="P86" s="72">
+        <v>3.532</v>
+      </c>
+      <c r="Q86" s="72">
+        <f t="shared" ref="Q86" si="72">N86*P86</f>
+        <v>74.171999999999997</v>
+      </c>
+      <c r="R86" s="69"/>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
-      <c r="B87" s="50">
-        <f t="shared" si="61"/>
-        <v>78</v>
-      </c>
-      <c r="C87" s="78" t="s">
-        <v>281</v>
-      </c>
-      <c r="D87" s="83" t="s">
-        <v>393</v>
-      </c>
-      <c r="E87" s="79" t="s">
-        <v>445</v>
-      </c>
-      <c r="F87" s="79" t="s">
-        <v>265</v>
-      </c>
-      <c r="G87" s="79" t="s">
-        <v>361</v>
-      </c>
-      <c r="H87" s="98" t="s">
-        <v>214</v>
-      </c>
-      <c r="I87" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="J87" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="K87" s="80" t="s">
-        <v>267</v>
-      </c>
-      <c r="L87" s="79">
-        <v>1</v>
-      </c>
-      <c r="M87" s="73">
-        <f t="shared" si="57"/>
-        <v>20</v>
-      </c>
-      <c r="N87" s="73">
-        <v>21</v>
-      </c>
-      <c r="O87" s="81" t="s">
-        <v>362</v>
-      </c>
-      <c r="P87" s="73">
-        <v>3.532</v>
-      </c>
-      <c r="Q87" s="73">
-        <f t="shared" ref="Q87" si="74">N87*P87</f>
-        <v>74.171999999999997</v>
-      </c>
-      <c r="R87" s="70"/>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B87" s="32"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E87" s="34"/>
+      <c r="F87" s="35"/>
+      <c r="G87" s="36"/>
+      <c r="H87" s="35"/>
+      <c r="I87" s="35"/>
+      <c r="J87" s="35"/>
+      <c r="K87" s="36"/>
+      <c r="L87" s="36"/>
+      <c r="M87" s="36"/>
+      <c r="N87" s="36"/>
+      <c r="O87" s="61" t="s">
+        <v>355</v>
+      </c>
+      <c r="P87" s="59"/>
+      <c r="Q87" s="59">
+        <f>SUM(Q10:Q86)</f>
+        <v>978.1422</v>
+      </c>
+      <c r="R87" s="41"/>
+    </row>
+    <row r="88" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
-      <c r="B88" s="32"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="E88" s="34"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="36"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
-      <c r="J88" s="35"/>
-      <c r="K88" s="36"/>
-      <c r="L88" s="36"/>
-      <c r="M88" s="36"/>
-      <c r="N88" s="36"/>
+      <c r="B88" s="24"/>
+      <c r="C88" s="49"/>
+      <c r="D88" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9"/>
+      <c r="G88" s="9"/>
+      <c r="H88" s="9"/>
+      <c r="I88" s="9"/>
+      <c r="J88" s="9"/>
+      <c r="K88" s="9"/>
+      <c r="L88" s="9"/>
+      <c r="M88" s="9"/>
+      <c r="N88" s="9"/>
       <c r="O88" s="62" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="P88" s="60"/>
-      <c r="Q88" s="60">
-        <f>SUM(Q10:Q87)</f>
-        <v>970.48620000000005</v>
-      </c>
-      <c r="R88" s="41"/>
-    </row>
-    <row r="89" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q88" s="105">
+        <f>Q87/20</f>
+        <v>48.907110000000003</v>
+      </c>
+      <c r="R88" s="42"/>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
-      <c r="B89" s="24"/>
-      <c r="C89" s="49"/>
-      <c r="D89" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E89" s="9"/>
-      <c r="F89" s="9"/>
-      <c r="G89" s="9"/>
-      <c r="H89" s="9"/>
-      <c r="I89" s="9"/>
-      <c r="J89" s="9"/>
-      <c r="K89" s="9"/>
-      <c r="L89" s="9"/>
-      <c r="M89" s="9"/>
-      <c r="N89" s="9"/>
-      <c r="O89" s="63" t="s">
-        <v>365</v>
-      </c>
-      <c r="P89" s="61"/>
-      <c r="Q89" s="107">
-        <f>Q88/20</f>
-        <v>48.52431</v>
-      </c>
-      <c r="R89" s="42"/>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A91" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7308,22 +7248,22 @@
     <hyperlink ref="O31" r:id="rId21"/>
     <hyperlink ref="O32" r:id="rId22"/>
     <hyperlink ref="O33" r:id="rId23"/>
-    <hyperlink ref="O34" r:id="rId24"/>
+    <hyperlink ref="O36" r:id="rId24"/>
     <hyperlink ref="O37" r:id="rId25"/>
     <hyperlink ref="O38" r:id="rId26"/>
-    <hyperlink ref="O39" r:id="rId27"/>
+    <hyperlink ref="O40" r:id="rId27"/>
     <hyperlink ref="O41" r:id="rId28"/>
-    <hyperlink ref="O42" r:id="rId29"/>
-    <hyperlink ref="O45" r:id="rId30"/>
-    <hyperlink ref="O46" r:id="rId31"/>
-    <hyperlink ref="O47" r:id="rId32"/>
+    <hyperlink ref="O45" r:id="rId29"/>
+    <hyperlink ref="O46" r:id="rId30"/>
+    <hyperlink ref="O47" r:id="rId31"/>
+    <hyperlink ref="O51" r:id="rId32"/>
     <hyperlink ref="O52" r:id="rId33"/>
     <hyperlink ref="O53" r:id="rId34"/>
     <hyperlink ref="O54" r:id="rId35"/>
     <hyperlink ref="O55" r:id="rId36"/>
     <hyperlink ref="O56" r:id="rId37"/>
-    <hyperlink ref="O57" r:id="rId38"/>
-    <hyperlink ref="O69" r:id="rId39"/>
+    <hyperlink ref="O68" r:id="rId38"/>
+    <hyperlink ref="O59" r:id="rId39"/>
     <hyperlink ref="O60" r:id="rId40"/>
     <hyperlink ref="O61" r:id="rId41"/>
     <hyperlink ref="O62" r:id="rId42"/>
@@ -7332,12 +7272,12 @@
     <hyperlink ref="O65" r:id="rId45"/>
     <hyperlink ref="O66" r:id="rId46"/>
     <hyperlink ref="O67" r:id="rId47"/>
-    <hyperlink ref="O68" r:id="rId48"/>
+    <hyperlink ref="O69" r:id="rId48"/>
     <hyperlink ref="O70" r:id="rId49"/>
     <hyperlink ref="O71" r:id="rId50"/>
-    <hyperlink ref="O72" r:id="rId51"/>
-    <hyperlink ref="O75" r:id="rId52"/>
-    <hyperlink ref="O73" r:id="rId53"/>
+    <hyperlink ref="O74" r:id="rId51"/>
+    <hyperlink ref="O72" r:id="rId52"/>
+    <hyperlink ref="O76" r:id="rId53"/>
     <hyperlink ref="O77" r:id="rId54"/>
     <hyperlink ref="O78" r:id="rId55"/>
     <hyperlink ref="O79" r:id="rId56"/>
@@ -7346,23 +7286,22 @@
     <hyperlink ref="O82" r:id="rId59"/>
     <hyperlink ref="O83" r:id="rId60"/>
     <hyperlink ref="O84" r:id="rId61"/>
-    <hyperlink ref="O85" r:id="rId62"/>
-    <hyperlink ref="O87" r:id="rId63"/>
-    <hyperlink ref="O86" r:id="rId64"/>
-    <hyperlink ref="O59" r:id="rId65"/>
-    <hyperlink ref="O10" r:id="rId66"/>
-    <hyperlink ref="O51" r:id="rId67"/>
-    <hyperlink ref="O76" r:id="rId68"/>
-    <hyperlink ref="O58" r:id="rId69"/>
-    <hyperlink ref="O35" r:id="rId70"/>
-    <hyperlink ref="O36" r:id="rId71"/>
-    <hyperlink ref="O40" r:id="rId72"/>
-    <hyperlink ref="O43" r:id="rId73"/>
-    <hyperlink ref="O44" r:id="rId74"/>
-    <hyperlink ref="O49" r:id="rId75"/>
+    <hyperlink ref="O86" r:id="rId62"/>
+    <hyperlink ref="O85" r:id="rId63"/>
+    <hyperlink ref="O58" r:id="rId64"/>
+    <hyperlink ref="O10" r:id="rId65"/>
+    <hyperlink ref="O75" r:id="rId66"/>
+    <hyperlink ref="O57" r:id="rId67"/>
+    <hyperlink ref="O34" r:id="rId68"/>
+    <hyperlink ref="O35" r:id="rId69"/>
+    <hyperlink ref="O39" r:id="rId70"/>
+    <hyperlink ref="O42" r:id="rId71"/>
+    <hyperlink ref="O44" r:id="rId72"/>
+    <hyperlink ref="O49" r:id="rId73"/>
+    <hyperlink ref="O43" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId76"/>
-  <drawing r:id="rId77"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId75"/>
+  <drawing r:id="rId76"/>
 </worksheet>
 </file>